--- a/Koszty/P&L_koszty_ROP.xlsx
+++ b/Koszty/P&L_koszty_ROP.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30117"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://studmsugedupl-my.sharepoint.com/personal/a_mazur_177_studms_ug_edu_pl/Documents/Dokumenty/Praca/P&amp;L/PiL_excel/Koszty/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://avistapl-my.sharepoint.com/personal/kp_avistapl_onmicrosoft_com/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7E3B7DFB-3AC5-47E9-A4B8-5131C45FBE77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0B23F104-24AC-4594-A282-457C8B61F72A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="16875" yWindow="1845" windowWidth="8970" windowHeight="8415" activeTab="1" xr2:uid="{15F9F442-F66C-4C0E-97EA-1DEECE69BD92}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{15F9F442-F66C-4C0E-97EA-1DEECE69BD92}"/>
   </bookViews>
   <sheets>
     <sheet name="2026" sheetId="4" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="21">
   <si>
     <t>WYNAGRODZENIA Z UMOWY (BEZ DODATKÓW)</t>
   </si>
@@ -96,6 +96,9 @@
     <t>UBEZPIECZENIE AUTOMATÓW</t>
   </si>
   <si>
+    <t>mzk opole</t>
+  </si>
+  <si>
     <t>SUMA za 12 msc</t>
   </si>
 </sst>
@@ -107,7 +110,7 @@
     <numFmt numFmtId="8" formatCode="#,##0.00\ &quot;zł&quot;;[Red]\-#,##0.00\ &quot;zł&quot;"/>
     <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;zł&quot;"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -252,39 +255,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="8" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="8" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="8" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="8" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="8" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="8" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -297,12 +267,45 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="8" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="8" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normalny" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="2">
     <dxf>
@@ -656,7 +659,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F0F0C55-82FF-4757-A5C6-BA3AD4086787}">
   <dimension ref="B2:W162"/>
-  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="2" max="2" width="15.5703125" customWidth="1"/>
     <col min="3" max="3" width="10.28515625" customWidth="1"/>
@@ -676,20 +679,20 @@
     <col min="23" max="23" width="13.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:23" x14ac:dyDescent="0.25">
-      <c r="B2" s="26" t="s">
+    <row r="2" spans="2:23" ht="14.45">
+      <c r="B2" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
       <c r="E2" s="3"/>
     </row>
-    <row r="3" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:23" ht="14.45">
       <c r="B3" s="1"/>
-      <c r="C3" s="27" t="s">
+      <c r="C3" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="28"/>
+      <c r="D3" s="17"/>
       <c r="E3" s="1"/>
       <c r="K3" s="7"/>
       <c r="L3" s="7"/>
@@ -705,13 +708,13 @@
       <c r="V3" s="7"/>
       <c r="W3" s="8"/>
     </row>
-    <row r="4" spans="2:23" x14ac:dyDescent="0.25">
-      <c r="B4" s="29" t="s">
+    <row r="4" spans="2:23" ht="14.45">
+      <c r="B4" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="29"/>
-      <c r="D4" s="29"/>
-      <c r="E4" s="29"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
       <c r="K4" s="7"/>
       <c r="L4" s="7"/>
       <c r="M4" s="7"/>
@@ -726,14 +729,14 @@
       <c r="V4" s="7"/>
       <c r="W4" s="8"/>
     </row>
-    <row r="5" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:23" ht="14.45">
       <c r="B5" s="2">
         <v>46023</v>
       </c>
-      <c r="C5" s="18">
+      <c r="C5" s="19">
         <v>48030.92</v>
       </c>
-      <c r="D5" s="19"/>
+      <c r="D5" s="20"/>
       <c r="E5" s="10"/>
       <c r="K5" s="10"/>
       <c r="L5" s="10"/>
@@ -749,52 +752,54 @@
       <c r="V5" s="10"/>
       <c r="W5" s="10"/>
     </row>
-    <row r="6" spans="2:23" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:23" ht="14.45" customHeight="1">
       <c r="B6" s="2">
         <v>46054</v>
       </c>
-      <c r="C6" s="18">
+      <c r="C6" s="19">
         <v>48017.66</v>
       </c>
-      <c r="D6" s="19"/>
+      <c r="D6" s="20"/>
       <c r="E6" s="10"/>
     </row>
-    <row r="7" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:23" ht="14.45">
       <c r="B7" s="2">
         <v>46082</v>
       </c>
-      <c r="C7" s="18">
+      <c r="C7" s="19">
         <v>48004</v>
       </c>
-      <c r="D7" s="19"/>
+      <c r="D7" s="20"/>
       <c r="E7" s="10"/>
     </row>
-    <row r="8" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:23" ht="14.45">
       <c r="B8" s="2">
         <v>46113</v>
       </c>
-      <c r="C8" s="18"/>
-      <c r="D8" s="19"/>
+      <c r="C8" s="19">
+        <v>48052.01</v>
+      </c>
+      <c r="D8" s="20"/>
       <c r="E8" s="10"/>
     </row>
-    <row r="9" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:23" ht="14.45">
       <c r="B9" s="2">
         <v>46143</v>
       </c>
-      <c r="C9" s="18"/>
-      <c r="D9" s="19"/>
+      <c r="C9" s="19"/>
+      <c r="D9" s="20"/>
       <c r="E9" s="10"/>
       <c r="F9" s="4">
         <f>SUM(C5:D16)</f>
-        <v>144052.58000000002</v>
-      </c>
-    </row>
-    <row r="10" spans="2:23" x14ac:dyDescent="0.25">
+        <v>192104.59000000003</v>
+      </c>
+    </row>
+    <row r="10" spans="2:23" ht="14.45">
       <c r="B10" s="2">
         <v>46174</v>
       </c>
-      <c r="C10" s="18"/>
-      <c r="D10" s="19"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="20"/>
       <c r="E10" s="10"/>
       <c r="J10" t="s">
         <v>3</v>
@@ -806,12 +811,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:23" ht="14.45">
       <c r="B11" s="2">
         <v>46204</v>
       </c>
-      <c r="C11" s="18"/>
-      <c r="D11" s="19"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="20"/>
       <c r="E11" s="10"/>
       <c r="I11" s="9">
         <v>46023</v>
@@ -832,12 +837,12 @@
         <v>1241.0915044247788</v>
       </c>
     </row>
-    <row r="12" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:23" ht="14.45">
       <c r="B12" s="2">
         <v>46235</v>
       </c>
-      <c r="C12" s="18"/>
-      <c r="D12" s="19"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="20"/>
       <c r="E12" s="10"/>
       <c r="I12" s="9">
         <v>46054</v>
@@ -851,12 +856,12 @@
         <v>24000</v>
       </c>
     </row>
-    <row r="13" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:23" ht="14.45">
       <c r="B13" s="2">
         <v>46266</v>
       </c>
-      <c r="C13" s="18"/>
-      <c r="D13" s="19"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="20"/>
       <c r="E13" s="10"/>
       <c r="I13" s="9">
         <v>46082</v>
@@ -870,31 +875,31 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:23" ht="14.45">
       <c r="B14" s="2">
         <v>46296</v>
       </c>
-      <c r="C14" s="18"/>
-      <c r="D14" s="19"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="20"/>
       <c r="E14" s="10"/>
       <c r="I14" s="9">
         <v>46113</v>
       </c>
       <c r="J14" s="4">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>95371.05</v>
       </c>
       <c r="K14" s="4">
         <f>J98</f>
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:23" ht="14.45">
       <c r="B15" s="2">
         <v>46327</v>
       </c>
-      <c r="C15" s="18"/>
-      <c r="D15" s="19"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="20"/>
       <c r="E15" s="10"/>
       <c r="I15" s="9">
         <v>46143</v>
@@ -908,12 +913,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:23" ht="14.45">
       <c r="B16" s="2">
         <v>46357</v>
       </c>
-      <c r="C16" s="18"/>
-      <c r="D16" s="19"/>
+      <c r="C16" s="19"/>
+      <c r="D16" s="20"/>
       <c r="E16" s="10"/>
       <c r="I16" s="9">
         <v>46174</v>
@@ -927,7 +932,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:11" ht="14.45">
       <c r="B17" s="9"/>
       <c r="C17" s="5"/>
       <c r="D17" s="6"/>
@@ -944,7 +949,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:11" ht="14.45">
       <c r="I18" s="9">
         <v>46235</v>
       </c>
@@ -957,12 +962,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B19" s="15" t="s">
+    <row r="19" spans="2:11" ht="14.45">
+      <c r="B19" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="C19" s="16"/>
-      <c r="D19" s="17"/>
+      <c r="C19" s="22"/>
+      <c r="D19" s="23"/>
       <c r="I19" s="9">
         <v>46266</v>
       </c>
@@ -975,14 +980,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:11" ht="14.45">
       <c r="B20" s="2">
         <v>46023</v>
       </c>
-      <c r="C20" s="18">
+      <c r="C20" s="19">
         <v>17862.419999999998</v>
       </c>
-      <c r="D20" s="19"/>
+      <c r="D20" s="20"/>
       <c r="I20" s="9">
         <v>46296</v>
       </c>
@@ -995,14 +1000,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:11" ht="14.45">
       <c r="B21" s="2">
         <v>46054</v>
       </c>
-      <c r="C21" s="18">
+      <c r="C21" s="19">
         <v>13054.2</v>
       </c>
-      <c r="D21" s="19"/>
+      <c r="D21" s="20"/>
       <c r="I21" s="9">
         <v>46327</v>
       </c>
@@ -1015,17 +1020,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:11" ht="14.45">
       <c r="B22" s="2">
         <v>46082</v>
       </c>
-      <c r="C22" s="18">
+      <c r="C22" s="19">
         <v>18097.5</v>
       </c>
-      <c r="D22" s="19"/>
+      <c r="D22" s="20"/>
       <c r="F22" s="4">
         <f>SUM(C20:D31)</f>
-        <v>49014.119999999995</v>
+        <v>66833.16</v>
       </c>
       <c r="I22" s="9">
         <v>46357</v>
@@ -1039,477 +1044,485 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:11" ht="14.45">
       <c r="B23" s="2">
         <v>46113</v>
       </c>
-      <c r="C23" s="18"/>
-      <c r="D23" s="19"/>
+      <c r="C23" s="19">
+        <v>17819.04</v>
+      </c>
+      <c r="D23" s="20"/>
       <c r="F23" s="4"/>
       <c r="I23" s="9"/>
     </row>
-    <row r="24" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:11" ht="14.45">
       <c r="B24" s="2">
         <v>46143</v>
       </c>
-      <c r="C24" s="18"/>
-      <c r="D24" s="19"/>
+      <c r="C24" s="19"/>
+      <c r="D24" s="20"/>
       <c r="F24" s="4"/>
       <c r="I24" s="9"/>
     </row>
-    <row r="25" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:11" ht="14.45">
       <c r="B25" s="2">
         <v>46174</v>
       </c>
-      <c r="C25" s="18"/>
-      <c r="D25" s="19"/>
+      <c r="C25" s="19"/>
+      <c r="D25" s="20"/>
       <c r="F25" s="4"/>
     </row>
-    <row r="26" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:11" ht="14.45">
       <c r="B26" s="2">
         <v>46204</v>
       </c>
-      <c r="C26" s="18"/>
-      <c r="D26" s="19"/>
+      <c r="C26" s="19"/>
+      <c r="D26" s="20"/>
       <c r="F26" s="4"/>
     </row>
-    <row r="27" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:11" ht="14.45">
       <c r="B27" s="2">
         <v>46235</v>
       </c>
-      <c r="C27" s="18"/>
-      <c r="D27" s="19"/>
+      <c r="C27" s="19"/>
+      <c r="D27" s="20"/>
       <c r="F27" s="4"/>
     </row>
-    <row r="28" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:11" ht="14.45">
       <c r="B28" s="2">
         <v>46266</v>
       </c>
-      <c r="C28" s="18"/>
-      <c r="D28" s="19"/>
+      <c r="C28" s="19"/>
+      <c r="D28" s="20"/>
       <c r="F28" s="4"/>
     </row>
-    <row r="29" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:11" ht="14.45">
       <c r="B29" s="2">
         <v>46296</v>
       </c>
-      <c r="C29" s="18"/>
-      <c r="D29" s="19"/>
+      <c r="C29" s="19"/>
+      <c r="D29" s="20"/>
       <c r="F29" s="4"/>
     </row>
-    <row r="30" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:11" ht="14.45">
       <c r="B30" s="2">
         <v>46327</v>
       </c>
-      <c r="C30" s="18"/>
-      <c r="D30" s="19"/>
+      <c r="C30" s="19"/>
+      <c r="D30" s="20"/>
       <c r="F30" s="4"/>
     </row>
-    <row r="31" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:11" ht="14.45">
       <c r="B31" s="2">
         <v>46357</v>
       </c>
-      <c r="C31" s="18"/>
-      <c r="D31" s="19"/>
+      <c r="C31" s="19"/>
+      <c r="D31" s="20"/>
       <c r="F31" s="4"/>
     </row>
-    <row r="32" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:11" ht="14.45">
       <c r="B32" s="9"/>
       <c r="C32" s="5"/>
       <c r="D32" s="6"/>
       <c r="F32" s="4"/>
     </row>
-    <row r="34" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B34" s="15" t="s">
+    <row r="34" spans="2:9" ht="14.45">
+      <c r="B34" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="C34" s="16"/>
-      <c r="D34" s="17"/>
-    </row>
-    <row r="35" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="C34" s="22"/>
+      <c r="D34" s="23"/>
+    </row>
+    <row r="35" spans="2:9" ht="14.45">
       <c r="B35" s="2">
         <v>46023</v>
       </c>
-      <c r="C35" s="18">
+      <c r="C35" s="19">
         <v>9326.02</v>
       </c>
-      <c r="D35" s="19"/>
-    </row>
-    <row r="36" spans="2:9" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D35" s="20"/>
+    </row>
+    <row r="36" spans="2:9" ht="14.45" customHeight="1">
       <c r="B36" s="2">
         <v>46054</v>
       </c>
-      <c r="C36" s="18">
+      <c r="C36" s="19">
         <v>9250.51</v>
       </c>
-      <c r="D36" s="19"/>
-    </row>
-    <row r="37" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="D36" s="20"/>
+    </row>
+    <row r="37" spans="2:9" ht="14.45">
       <c r="B37" s="2">
         <v>46082</v>
       </c>
-      <c r="C37" s="18">
+      <c r="C37" s="19">
         <v>6974.05</v>
       </c>
-      <c r="D37" s="19"/>
+      <c r="D37" s="20"/>
       <c r="F37" s="4">
         <f>SUM(C35:D46)</f>
-        <v>25550.579999999998</v>
-      </c>
-    </row>
-    <row r="38" spans="2:9" x14ac:dyDescent="0.25">
+        <v>34947.64</v>
+      </c>
+    </row>
+    <row r="38" spans="2:9" ht="14.45">
       <c r="B38" s="2">
         <v>46113</v>
       </c>
-      <c r="C38" s="18"/>
-      <c r="D38" s="19"/>
+      <c r="C38" s="19">
+        <v>9397.06</v>
+      </c>
+      <c r="D38" s="20"/>
       <c r="F38" s="4"/>
       <c r="I38" s="4"/>
     </row>
-    <row r="39" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:9" ht="14.45">
       <c r="B39" s="2">
         <v>46143</v>
       </c>
-      <c r="C39" s="18"/>
-      <c r="D39" s="19"/>
+      <c r="C39" s="19"/>
+      <c r="D39" s="20"/>
       <c r="F39" s="4"/>
       <c r="I39" s="4"/>
     </row>
-    <row r="40" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:9" ht="14.45">
       <c r="B40" s="2">
         <v>46174</v>
       </c>
-      <c r="C40" s="18"/>
-      <c r="D40" s="19"/>
+      <c r="C40" s="19"/>
+      <c r="D40" s="20"/>
       <c r="F40" s="4"/>
     </row>
-    <row r="41" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:9" ht="14.45">
       <c r="B41" s="2">
         <v>46204</v>
       </c>
-      <c r="C41" s="18"/>
-      <c r="D41" s="19"/>
+      <c r="C41" s="19"/>
+      <c r="D41" s="20"/>
       <c r="F41" s="4"/>
     </row>
-    <row r="42" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:9" ht="14.45">
       <c r="B42" s="2">
         <v>46235</v>
       </c>
-      <c r="C42" s="18"/>
-      <c r="D42" s="19"/>
+      <c r="C42" s="19"/>
+      <c r="D42" s="20"/>
       <c r="F42" s="4"/>
     </row>
-    <row r="43" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:9" ht="14.45">
       <c r="B43" s="2">
         <v>46266</v>
       </c>
-      <c r="C43" s="18"/>
-      <c r="D43" s="19"/>
+      <c r="C43" s="19"/>
+      <c r="D43" s="20"/>
       <c r="F43" s="4"/>
     </row>
-    <row r="44" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:9" ht="14.45">
       <c r="B44" s="2">
         <v>46296</v>
       </c>
-      <c r="C44" s="18"/>
-      <c r="D44" s="19"/>
+      <c r="C44" s="19"/>
+      <c r="D44" s="20"/>
       <c r="F44" s="4"/>
     </row>
-    <row r="45" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:9" ht="14.45">
       <c r="B45" s="2">
         <v>46327</v>
       </c>
-      <c r="C45" s="18"/>
-      <c r="D45" s="19"/>
+      <c r="C45" s="19"/>
+      <c r="D45" s="20"/>
       <c r="F45" s="4"/>
     </row>
-    <row r="46" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:9" ht="14.45">
       <c r="B46" s="2">
         <v>46357</v>
       </c>
-      <c r="C46" s="18"/>
-      <c r="D46" s="19"/>
+      <c r="C46" s="19"/>
+      <c r="D46" s="20"/>
       <c r="F46" s="4"/>
     </row>
-    <row r="47" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:9" ht="14.45">
       <c r="B47" s="9"/>
       <c r="C47" s="5"/>
       <c r="D47" s="6"/>
       <c r="F47" s="4"/>
     </row>
-    <row r="49" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B49" s="15" t="s">
+    <row r="49" spans="2:6" ht="14.45">
+      <c r="B49" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="C49" s="16"/>
-      <c r="D49" s="17"/>
-    </row>
-    <row r="50" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C49" s="22"/>
+      <c r="D49" s="23"/>
+    </row>
+    <row r="50" spans="2:6" ht="14.45">
       <c r="B50" s="2">
         <v>46023</v>
       </c>
-      <c r="C50" s="18">
+      <c r="C50" s="19">
         <v>55463.63</v>
       </c>
-      <c r="D50" s="19"/>
-    </row>
-    <row r="51" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="D50" s="20"/>
+    </row>
+    <row r="51" spans="2:6">
       <c r="B51" s="2">
         <v>46054</v>
       </c>
-      <c r="C51" s="18">
+      <c r="C51" s="19">
         <v>55463.63</v>
       </c>
-      <c r="D51" s="19"/>
-    </row>
-    <row r="52" spans="2:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D51" s="20"/>
+    </row>
+    <row r="52" spans="2:6" ht="14.45" customHeight="1">
       <c r="B52" s="2">
         <v>46082</v>
       </c>
-      <c r="C52" s="18">
+      <c r="C52" s="19">
         <v>55463.63</v>
       </c>
-      <c r="D52" s="19"/>
+      <c r="D52" s="20"/>
       <c r="F52" s="4">
         <f>SUM(C50:D61)</f>
-        <v>166390.88999999998</v>
-      </c>
-    </row>
-    <row r="53" spans="2:6" x14ac:dyDescent="0.25">
+        <v>224236.49</v>
+      </c>
+    </row>
+    <row r="53" spans="2:6">
       <c r="B53" s="2">
         <v>46113</v>
       </c>
-      <c r="C53" s="18"/>
-      <c r="D53" s="19"/>
+      <c r="C53" s="19">
+        <v>57845.599999999999</v>
+      </c>
+      <c r="D53" s="20"/>
       <c r="F53" s="4"/>
     </row>
-    <row r="54" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:6" ht="14.45">
       <c r="B54" s="2">
         <v>46143</v>
       </c>
-      <c r="C54" s="18"/>
-      <c r="D54" s="19"/>
+      <c r="C54" s="19"/>
+      <c r="D54" s="20"/>
       <c r="F54" s="4"/>
     </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:6" ht="14.45">
       <c r="B55" s="2">
         <v>46174</v>
       </c>
-      <c r="C55" s="18"/>
-      <c r="D55" s="19"/>
+      <c r="C55" s="19"/>
+      <c r="D55" s="20"/>
       <c r="F55" s="4"/>
     </row>
-    <row r="56" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:6" ht="14.45">
       <c r="B56" s="2">
         <v>46204</v>
       </c>
-      <c r="C56" s="18"/>
-      <c r="D56" s="19"/>
+      <c r="C56" s="19"/>
+      <c r="D56" s="20"/>
       <c r="F56" s="4"/>
     </row>
-    <row r="57" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:6" ht="14.45">
       <c r="B57" s="2">
         <v>46235</v>
       </c>
-      <c r="C57" s="18"/>
-      <c r="D57" s="19"/>
+      <c r="C57" s="19"/>
+      <c r="D57" s="20"/>
       <c r="F57" s="4"/>
     </row>
-    <row r="58" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:6" ht="14.45">
       <c r="B58" s="2">
         <v>46266</v>
       </c>
-      <c r="C58" s="18"/>
-      <c r="D58" s="19"/>
+      <c r="C58" s="19"/>
+      <c r="D58" s="20"/>
       <c r="F58" s="4"/>
     </row>
-    <row r="59" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:6" ht="14.45">
       <c r="B59" s="2">
         <v>46296</v>
       </c>
-      <c r="C59" s="18"/>
-      <c r="D59" s="19"/>
+      <c r="C59" s="19"/>
+      <c r="D59" s="20"/>
       <c r="F59" s="4"/>
     </row>
-    <row r="60" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:6" ht="14.45">
       <c r="B60" s="2">
         <v>46327</v>
       </c>
-      <c r="C60" s="18"/>
-      <c r="D60" s="19"/>
+      <c r="C60" s="19"/>
+      <c r="D60" s="20"/>
       <c r="F60" s="4"/>
     </row>
-    <row r="61" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:6" ht="14.45">
       <c r="B61" s="2">
         <v>46357</v>
       </c>
-      <c r="C61" s="18"/>
-      <c r="D61" s="19"/>
+      <c r="C61" s="19"/>
+      <c r="D61" s="20"/>
       <c r="F61" s="4"/>
     </row>
-    <row r="64" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B64" s="15" t="s">
+    <row r="64" spans="2:6" ht="14.45">
+      <c r="B64" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="C64" s="16"/>
-      <c r="D64" s="17"/>
-    </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="C64" s="22"/>
+      <c r="D64" s="23"/>
+    </row>
+    <row r="65" spans="2:11" ht="14.45">
       <c r="B65" s="2">
         <v>46023</v>
       </c>
-      <c r="C65" s="18">
+      <c r="C65" s="19">
         <v>7484.38</v>
       </c>
-      <c r="D65" s="19"/>
-    </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="D65" s="20"/>
+    </row>
+    <row r="66" spans="2:11" ht="14.45">
       <c r="B66" s="2">
         <v>46054</v>
       </c>
-      <c r="C66" s="18">
+      <c r="C66" s="19">
         <v>5977.18</v>
       </c>
-      <c r="D66" s="19"/>
-    </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="D66" s="20"/>
+    </row>
+    <row r="67" spans="2:11" ht="14.45">
       <c r="B67" s="2">
         <v>46082</v>
       </c>
-      <c r="C67" s="18">
+      <c r="C67" s="19">
         <v>7206.57</v>
       </c>
-      <c r="D67" s="19"/>
+      <c r="D67" s="20"/>
       <c r="F67" s="4">
         <f>SUM(C65:D76)</f>
-        <v>20668.13</v>
-      </c>
-    </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.25">
+        <v>27940.11</v>
+      </c>
+    </row>
+    <row r="68" spans="2:11" ht="14.45">
       <c r="B68" s="2">
         <v>46113</v>
       </c>
-      <c r="C68" s="18"/>
-      <c r="D68" s="19"/>
-    </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="C68" s="19">
+        <v>7271.98</v>
+      </c>
+      <c r="D68" s="20"/>
+    </row>
+    <row r="69" spans="2:11" ht="14.45">
       <c r="B69" s="2">
         <v>46143</v>
       </c>
-      <c r="C69" s="18"/>
-      <c r="D69" s="19"/>
-    </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="C69" s="19"/>
+      <c r="D69" s="20"/>
+    </row>
+    <row r="70" spans="2:11" ht="14.45">
       <c r="B70" s="2">
         <v>46174</v>
       </c>
-      <c r="C70" s="18"/>
-      <c r="D70" s="19"/>
-    </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="C70" s="19"/>
+      <c r="D70" s="20"/>
+    </row>
+    <row r="71" spans="2:11" ht="14.45">
       <c r="B71" s="2">
         <v>46204</v>
       </c>
-      <c r="C71" s="18"/>
-      <c r="D71" s="19"/>
-    </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="C71" s="19"/>
+      <c r="D71" s="20"/>
+    </row>
+    <row r="72" spans="2:11" ht="14.45">
       <c r="B72" s="2">
         <v>46235</v>
       </c>
-      <c r="C72" s="18"/>
-      <c r="D72" s="19"/>
-    </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="C72" s="19"/>
+      <c r="D72" s="20"/>
+    </row>
+    <row r="73" spans="2:11" ht="14.45">
       <c r="B73" s="2">
         <v>46266</v>
       </c>
-      <c r="C73" s="18"/>
-      <c r="D73" s="19"/>
-    </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="C73" s="19"/>
+      <c r="D73" s="20"/>
+    </row>
+    <row r="74" spans="2:11" ht="14.45">
       <c r="B74" s="2">
         <v>46296</v>
       </c>
-      <c r="C74" s="18"/>
-      <c r="D74" s="19"/>
-    </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="C74" s="19"/>
+      <c r="D74" s="20"/>
+    </row>
+    <row r="75" spans="2:11" ht="14.45">
       <c r="B75" s="2">
         <v>46327</v>
       </c>
-      <c r="C75" s="18"/>
-      <c r="D75" s="19"/>
-    </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="C75" s="19"/>
+      <c r="D75" s="20"/>
+    </row>
+    <row r="76" spans="2:11" ht="14.45">
       <c r="B76" s="2">
         <v>46357</v>
       </c>
-      <c r="C76" s="18"/>
-      <c r="D76" s="19"/>
-    </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="C76" s="19"/>
+      <c r="D76" s="20"/>
+    </row>
+    <row r="77" spans="2:11" ht="14.45">
       <c r="B77" s="9"/>
       <c r="C77" s="5"/>
       <c r="D77" s="5"/>
     </row>
-    <row r="78" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:11" ht="14.45">
       <c r="B78" s="9"/>
       <c r="C78" s="5"/>
       <c r="D78" s="5"/>
     </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B79" s="15" t="s">
+    <row r="79" spans="2:11" ht="14.45">
+      <c r="B79" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="C79" s="16"/>
-      <c r="D79" s="17"/>
-      <c r="I79" s="15" t="s">
+      <c r="C79" s="22"/>
+      <c r="D79" s="23"/>
+      <c r="I79" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="J79" s="16"/>
-      <c r="K79" s="17"/>
-    </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="J79" s="22"/>
+      <c r="K79" s="23"/>
+    </row>
+    <row r="80" spans="2:11" ht="14.45">
       <c r="B80" s="2">
         <v>46023</v>
       </c>
-      <c r="C80" s="18">
+      <c r="C80" s="19">
         <v>0</v>
       </c>
-      <c r="D80" s="19"/>
+      <c r="D80" s="20"/>
       <c r="I80" s="2">
         <v>46023</v>
       </c>
-      <c r="J80" s="18">
+      <c r="J80" s="19">
         <v>0</v>
       </c>
-      <c r="K80" s="19"/>
-    </row>
-    <row r="81" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="K80" s="20"/>
+    </row>
+    <row r="81" spans="2:16" ht="14.45">
       <c r="B81" s="2">
         <v>46054</v>
       </c>
-      <c r="C81" s="18">
+      <c r="C81" s="19">
         <v>0</v>
       </c>
-      <c r="D81" s="19"/>
+      <c r="D81" s="20"/>
       <c r="I81" s="2">
         <v>46054</v>
       </c>
-      <c r="J81" s="18">
+      <c r="J81" s="19">
         <v>0</v>
       </c>
-      <c r="K81" s="19"/>
-    </row>
-    <row r="82" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="K81" s="20"/>
+    </row>
+    <row r="82" spans="2:16" ht="14.45">
       <c r="B82" s="2">
         <v>46082</v>
       </c>
-      <c r="C82" s="18">
+      <c r="C82" s="19">
         <v>0</v>
       </c>
-      <c r="D82" s="19"/>
+      <c r="D82" s="20"/>
       <c r="F82" s="4">
         <f>SUM(C80:D91)</f>
         <v>46880</v>
@@ -1517,834 +1530,933 @@
       <c r="I82" s="2">
         <v>46082</v>
       </c>
-      <c r="J82" s="18">
+      <c r="J82" s="19">
         <v>2735.48</v>
       </c>
-      <c r="K82" s="19"/>
-    </row>
-    <row r="83" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="K82" s="20"/>
+    </row>
+    <row r="83" spans="2:16" ht="14.45">
       <c r="B83" s="2">
         <v>46113</v>
       </c>
-      <c r="C83" s="18">
+      <c r="C83" s="19">
         <v>46880</v>
       </c>
-      <c r="D83" s="19"/>
+      <c r="D83" s="20"/>
       <c r="I83" s="2">
         <v>46113</v>
       </c>
-      <c r="J83" s="18">
+      <c r="J83" s="19">
         <f>5300/2</f>
         <v>2650</v>
       </c>
-      <c r="K83" s="19"/>
+      <c r="K83" s="20"/>
       <c r="M83" s="4"/>
     </row>
-    <row r="84" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:16" ht="14.45">
       <c r="B84" s="2">
         <v>46143</v>
       </c>
-      <c r="C84" s="18"/>
-      <c r="D84" s="19"/>
+      <c r="C84" s="19"/>
+      <c r="D84" s="20"/>
       <c r="I84" s="2">
         <v>46143</v>
       </c>
-      <c r="J84" s="18">
+      <c r="J84" s="19">
         <f t="shared" ref="J84:J91" si="2">5300/2</f>
         <v>2650</v>
       </c>
-      <c r="K84" s="19"/>
-    </row>
-    <row r="85" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="K84" s="20"/>
+    </row>
+    <row r="85" spans="2:16" ht="14.45">
       <c r="B85" s="2">
         <v>46174</v>
       </c>
-      <c r="C85" s="18"/>
-      <c r="D85" s="19"/>
+      <c r="C85" s="19"/>
+      <c r="D85" s="20"/>
       <c r="I85" s="2">
         <v>46174</v>
       </c>
-      <c r="J85" s="20">
+      <c r="J85" s="25">
         <f t="shared" si="2"/>
         <v>2650</v>
       </c>
-      <c r="K85" s="20"/>
-    </row>
-    <row r="86" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="K85" s="25"/>
+    </row>
+    <row r="86" spans="2:16" ht="14.45">
       <c r="B86" s="2">
         <v>46204</v>
       </c>
-      <c r="C86" s="18"/>
-      <c r="D86" s="19"/>
+      <c r="C86" s="19"/>
+      <c r="D86" s="20"/>
       <c r="I86" s="2">
         <v>46204</v>
       </c>
-      <c r="J86" s="20">
+      <c r="J86" s="25">
         <f t="shared" si="2"/>
         <v>2650</v>
       </c>
-      <c r="K86" s="20"/>
-    </row>
-    <row r="87" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="K86" s="25"/>
+    </row>
+    <row r="87" spans="2:16" ht="14.45">
       <c r="B87" s="2">
         <v>46235</v>
       </c>
-      <c r="C87" s="18"/>
-      <c r="D87" s="19"/>
+      <c r="C87" s="19"/>
+      <c r="D87" s="20"/>
       <c r="I87" s="2">
         <v>46235</v>
       </c>
-      <c r="J87" s="20">
+      <c r="J87" s="25">
         <f t="shared" si="2"/>
         <v>2650</v>
       </c>
-      <c r="K87" s="20"/>
-    </row>
-    <row r="88" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="K87" s="25"/>
+    </row>
+    <row r="88" spans="2:16" ht="14.45">
       <c r="B88" s="2">
         <v>46266</v>
       </c>
-      <c r="C88" s="18"/>
-      <c r="D88" s="19"/>
+      <c r="C88" s="19"/>
+      <c r="D88" s="20"/>
       <c r="I88" s="2">
         <v>46266</v>
       </c>
-      <c r="J88" s="20">
+      <c r="J88" s="25">
         <f t="shared" si="2"/>
         <v>2650</v>
       </c>
-      <c r="K88" s="20"/>
-    </row>
-    <row r="89" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="K88" s="25"/>
+    </row>
+    <row r="89" spans="2:16" ht="14.45">
       <c r="B89" s="2">
         <v>46296</v>
       </c>
-      <c r="C89" s="18"/>
-      <c r="D89" s="19"/>
+      <c r="C89" s="19"/>
+      <c r="D89" s="20"/>
       <c r="G89" s="4"/>
       <c r="H89" s="4"/>
       <c r="I89" s="2">
         <v>46296</v>
       </c>
-      <c r="J89" s="20">
+      <c r="J89" s="25">
         <f t="shared" si="2"/>
         <v>2650</v>
       </c>
-      <c r="K89" s="20"/>
-    </row>
-    <row r="90" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="K89" s="25"/>
+    </row>
+    <row r="90" spans="2:16" ht="14.45">
       <c r="B90" s="2">
         <v>46327</v>
       </c>
-      <c r="C90" s="18"/>
-      <c r="D90" s="19"/>
+      <c r="C90" s="19"/>
+      <c r="D90" s="20"/>
       <c r="I90" s="2">
         <v>46327</v>
       </c>
-      <c r="J90" s="20">
+      <c r="J90" s="25">
         <f t="shared" si="2"/>
         <v>2650</v>
       </c>
-      <c r="K90" s="20"/>
-    </row>
-    <row r="91" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="K90" s="25"/>
+    </row>
+    <row r="91" spans="2:16" ht="14.45">
       <c r="B91" s="2">
         <v>46357</v>
       </c>
-      <c r="C91" s="18"/>
-      <c r="D91" s="19"/>
+      <c r="C91" s="19"/>
+      <c r="D91" s="20"/>
       <c r="I91" s="2">
         <v>46357</v>
       </c>
-      <c r="J91" s="20">
+      <c r="J91" s="25">
         <f t="shared" si="2"/>
         <v>2650</v>
       </c>
-      <c r="K91" s="20"/>
-    </row>
-    <row r="92" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K91" s="25"/>
+    </row>
+    <row r="92" spans="2:16" ht="15.75" customHeight="1">
       <c r="B92" s="9"/>
       <c r="C92" s="5"/>
       <c r="D92" s="5"/>
       <c r="I92" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="J92" s="23">
+      <c r="J92" s="26">
         <f>SUM(J80:K91)</f>
         <v>26585.48</v>
       </c>
-      <c r="K92" s="24"/>
-    </row>
-    <row r="93" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K92" s="27"/>
+    </row>
+    <row r="93" spans="2:16" ht="15.75" customHeight="1">
       <c r="B93" s="9"/>
       <c r="C93" s="5"/>
       <c r="D93" s="5"/>
     </row>
-    <row r="94" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B94" s="15" t="s">
+    <row r="94" spans="2:16" ht="15.75" customHeight="1">
+      <c r="B94" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="C94" s="16"/>
-      <c r="D94" s="17"/>
-      <c r="I94" s="15" t="s">
+      <c r="C94" s="22"/>
+      <c r="D94" s="23"/>
+      <c r="I94" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="J94" s="16"/>
-      <c r="K94" s="17"/>
-      <c r="N94" s="15" t="s">
+      <c r="J94" s="22"/>
+      <c r="K94" s="23"/>
+      <c r="N94" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="O94" s="16"/>
-      <c r="P94" s="17"/>
-    </row>
-    <row r="95" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O94" s="22"/>
+      <c r="P94" s="23"/>
+    </row>
+    <row r="95" spans="2:16" ht="15.75" customHeight="1">
       <c r="B95" s="2">
         <v>46023</v>
       </c>
-      <c r="C95" s="18">
+      <c r="C95" s="19">
         <v>24970</v>
       </c>
-      <c r="D95" s="19"/>
+      <c r="D95" s="20"/>
       <c r="I95" s="2">
         <v>46023</v>
       </c>
-      <c r="J95" s="18">
+      <c r="J95" s="19">
         <v>0</v>
       </c>
-      <c r="K95" s="19"/>
+      <c r="K95" s="20"/>
       <c r="N95" s="2">
         <v>46023</v>
       </c>
-      <c r="O95" s="18">
+      <c r="O95" s="19">
         <f>44850+29500</f>
         <v>74350</v>
       </c>
-      <c r="P95" s="25"/>
-    </row>
-    <row r="96" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P95" s="24"/>
+    </row>
+    <row r="96" spans="2:16" ht="15.75" customHeight="1">
       <c r="B96" s="2">
         <v>46054</v>
       </c>
-      <c r="C96" s="18">
+      <c r="C96" s="19">
         <v>19107.400000000001</v>
       </c>
-      <c r="D96" s="19"/>
+      <c r="D96" s="20"/>
       <c r="I96" s="2">
         <v>46054</v>
       </c>
-      <c r="J96" s="18">
+      <c r="J96" s="19">
         <v>24000</v>
       </c>
-      <c r="K96" s="19"/>
+      <c r="K96" s="20"/>
       <c r="N96" s="2">
         <v>46054</v>
       </c>
-      <c r="O96" s="18">
+      <c r="O96" s="19">
         <v>29500</v>
       </c>
-      <c r="P96" s="25"/>
-    </row>
-    <row r="97" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P96" s="24"/>
+    </row>
+    <row r="97" spans="2:18" ht="15.75" customHeight="1">
       <c r="B97" s="2">
         <v>46082</v>
       </c>
-      <c r="C97" s="18">
+      <c r="C97" s="19">
         <v>26370</v>
       </c>
-      <c r="D97" s="19"/>
+      <c r="D97" s="20"/>
       <c r="F97" s="4">
         <f>SUM(C95:D106)</f>
-        <v>70447.399999999994</v>
+        <v>96467.4</v>
       </c>
       <c r="I97" s="2">
         <v>46082</v>
       </c>
-      <c r="J97" s="18">
+      <c r="J97" s="19">
         <v>0</v>
       </c>
-      <c r="K97" s="19"/>
+      <c r="K97" s="20"/>
       <c r="N97" s="2">
         <v>46082</v>
       </c>
-      <c r="O97" s="18">
+      <c r="O97" s="19">
         <v>29500</v>
       </c>
-      <c r="P97" s="25"/>
-    </row>
-    <row r="98" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P97" s="24"/>
+    </row>
+    <row r="98" spans="2:18" ht="15.75" customHeight="1">
       <c r="B98" s="2">
         <v>46113</v>
       </c>
-      <c r="C98" s="18"/>
-      <c r="D98" s="19"/>
+      <c r="C98" s="19">
+        <v>26020</v>
+      </c>
+      <c r="D98" s="20"/>
       <c r="I98" s="2">
         <v>46113</v>
       </c>
-      <c r="J98" s="18"/>
-      <c r="K98" s="19"/>
+      <c r="J98" s="19">
+        <v>0</v>
+      </c>
+      <c r="K98" s="20"/>
       <c r="N98" s="2">
         <v>46113</v>
       </c>
-      <c r="O98" s="18"/>
-      <c r="P98" s="25"/>
-    </row>
-    <row r="99" spans="2:18" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O98" s="19">
+        <v>29500</v>
+      </c>
+      <c r="P98" s="24"/>
+    </row>
+    <row r="99" spans="2:18" ht="15.6" customHeight="1">
       <c r="B99" s="2">
         <v>46143</v>
       </c>
-      <c r="C99" s="18"/>
-      <c r="D99" s="19"/>
+      <c r="C99" s="19"/>
+      <c r="D99" s="20"/>
       <c r="I99" s="2">
         <v>46143</v>
       </c>
-      <c r="J99" s="18"/>
-      <c r="K99" s="19"/>
+      <c r="J99" s="19"/>
+      <c r="K99" s="20"/>
       <c r="N99" s="2">
         <v>46143</v>
       </c>
-      <c r="O99" s="18"/>
-      <c r="P99" s="25"/>
-    </row>
-    <row r="100" spans="2:18" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O99" s="19"/>
+      <c r="P99" s="24"/>
+    </row>
+    <row r="100" spans="2:18" ht="15.6" customHeight="1">
       <c r="B100" s="2">
         <v>46174</v>
       </c>
-      <c r="C100" s="18"/>
-      <c r="D100" s="19"/>
+      <c r="C100" s="19"/>
+      <c r="D100" s="20"/>
       <c r="I100" s="2">
         <v>46174</v>
       </c>
-      <c r="J100" s="18"/>
-      <c r="K100" s="19"/>
+      <c r="J100" s="19"/>
+      <c r="K100" s="20"/>
       <c r="N100" s="2">
         <v>46174</v>
       </c>
-      <c r="O100" s="18"/>
-      <c r="P100" s="25"/>
-    </row>
-    <row r="101" spans="2:18" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O100" s="19"/>
+      <c r="P100" s="24"/>
+    </row>
+    <row r="101" spans="2:18" ht="15.6" customHeight="1">
       <c r="B101" s="2">
         <v>46204</v>
       </c>
-      <c r="C101" s="18"/>
-      <c r="D101" s="19"/>
+      <c r="C101" s="19"/>
+      <c r="D101" s="20"/>
       <c r="I101" s="2">
         <v>46204</v>
       </c>
-      <c r="J101" s="18"/>
-      <c r="K101" s="19"/>
+      <c r="J101" s="19"/>
+      <c r="K101" s="20"/>
       <c r="N101" s="2">
         <v>46204</v>
       </c>
-      <c r="O101" s="18"/>
-      <c r="P101" s="25"/>
-    </row>
-    <row r="102" spans="2:18" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O101" s="19"/>
+      <c r="P101" s="24"/>
+    </row>
+    <row r="102" spans="2:18" ht="15.6" customHeight="1">
       <c r="B102" s="2">
         <v>46235</v>
       </c>
-      <c r="C102" s="18"/>
-      <c r="D102" s="19"/>
+      <c r="C102" s="19"/>
+      <c r="D102" s="20"/>
       <c r="I102" s="2">
         <v>46235</v>
       </c>
-      <c r="J102" s="18"/>
-      <c r="K102" s="19"/>
+      <c r="J102" s="19"/>
+      <c r="K102" s="20"/>
       <c r="N102" s="2">
         <v>46235</v>
       </c>
-      <c r="O102" s="18"/>
-      <c r="P102" s="25"/>
-    </row>
-    <row r="103" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="O102" s="19"/>
+      <c r="P102" s="24"/>
+    </row>
+    <row r="103" spans="2:18" ht="14.45">
       <c r="B103" s="2">
         <v>46266</v>
       </c>
-      <c r="C103" s="18"/>
-      <c r="D103" s="19"/>
+      <c r="C103" s="19"/>
+      <c r="D103" s="20"/>
       <c r="I103" s="2">
         <v>46266</v>
       </c>
-      <c r="J103" s="18"/>
-      <c r="K103" s="19"/>
+      <c r="J103" s="19"/>
+      <c r="K103" s="20"/>
       <c r="N103" s="2">
         <v>46266</v>
       </c>
-      <c r="O103" s="18"/>
-      <c r="P103" s="25"/>
-    </row>
-    <row r="104" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="O103" s="19"/>
+      <c r="P103" s="24"/>
+    </row>
+    <row r="104" spans="2:18" ht="14.45">
       <c r="B104" s="2">
         <v>46296</v>
       </c>
-      <c r="C104" s="18"/>
-      <c r="D104" s="19"/>
+      <c r="C104" s="19"/>
+      <c r="D104" s="20"/>
       <c r="I104" s="2">
         <v>46296</v>
       </c>
-      <c r="J104" s="18"/>
-      <c r="K104" s="19"/>
+      <c r="J104" s="19"/>
+      <c r="K104" s="20"/>
       <c r="N104" s="2">
         <v>46296</v>
       </c>
-      <c r="O104" s="18"/>
-      <c r="P104" s="25"/>
-    </row>
-    <row r="105" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="O104" s="19"/>
+      <c r="P104" s="24"/>
+    </row>
+    <row r="105" spans="2:18" ht="14.45">
       <c r="B105" s="2">
         <v>46327</v>
       </c>
-      <c r="C105" s="18"/>
-      <c r="D105" s="19"/>
+      <c r="C105" s="19"/>
+      <c r="D105" s="20"/>
       <c r="I105" s="2">
         <v>46327</v>
       </c>
-      <c r="J105" s="18"/>
-      <c r="K105" s="19"/>
+      <c r="J105" s="19"/>
+      <c r="K105" s="20"/>
       <c r="N105" s="2">
         <v>46327</v>
       </c>
-      <c r="O105" s="18"/>
-      <c r="P105" s="19"/>
-    </row>
-    <row r="106" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O105" s="19"/>
+      <c r="P105" s="20"/>
+    </row>
+    <row r="106" spans="2:18" ht="15" customHeight="1">
       <c r="B106" s="2">
         <v>46357</v>
       </c>
-      <c r="C106" s="18"/>
-      <c r="D106" s="19"/>
+      <c r="C106" s="19"/>
+      <c r="D106" s="20"/>
       <c r="I106" s="2">
         <v>46357</v>
       </c>
-      <c r="J106" s="18"/>
-      <c r="K106" s="19"/>
+      <c r="J106" s="19"/>
+      <c r="K106" s="20"/>
       <c r="N106" s="2">
         <v>46357</v>
       </c>
-      <c r="O106" s="18"/>
-      <c r="P106" s="19"/>
-    </row>
-    <row r="107" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="O106" s="19"/>
+      <c r="P106" s="20"/>
+    </row>
+    <row r="107" spans="2:18" ht="14.45">
       <c r="B107" s="9"/>
       <c r="C107" s="5"/>
       <c r="D107" s="5"/>
       <c r="I107" t="s">
         <v>12</v>
       </c>
-      <c r="J107" s="23">
+      <c r="J107" s="26">
         <f>SUM(J95:K106)</f>
         <v>24000</v>
       </c>
-      <c r="K107" s="24"/>
+      <c r="K107" s="27"/>
       <c r="N107" t="s">
         <v>12</v>
       </c>
       <c r="O107" s="4">
         <f>SUM(O95:P106)</f>
-        <v>133350</v>
+        <v>162850</v>
       </c>
       <c r="R107" s="4"/>
     </row>
-    <row r="108" spans="2:18" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="2:18" ht="14.45" customHeight="1">
       <c r="B108" s="9"/>
       <c r="C108" s="5"/>
       <c r="D108" s="5"/>
     </row>
-    <row r="109" spans="2:18" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="2:18" ht="14.45" customHeight="1">
       <c r="B109" s="9"/>
       <c r="C109" s="5"/>
       <c r="D109" s="5"/>
     </row>
-    <row r="110" spans="2:18" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="2:18" ht="14.45" customHeight="1">
       <c r="B110" s="9"/>
       <c r="C110" s="5"/>
       <c r="D110" s="5"/>
     </row>
-    <row r="111" spans="2:18" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B111" s="15" t="s">
+    <row r="111" spans="2:18" ht="14.45" customHeight="1">
+      <c r="B111" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="C111" s="16"/>
-      <c r="D111" s="17"/>
-    </row>
-    <row r="112" spans="2:18" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C111" s="22"/>
+      <c r="D111" s="23"/>
+    </row>
+    <row r="112" spans="2:18" ht="14.45" customHeight="1">
       <c r="B112" s="2">
         <v>46023</v>
       </c>
-      <c r="C112" s="18">
+      <c r="C112" s="19">
         <v>18064</v>
       </c>
-      <c r="D112" s="19"/>
+      <c r="D112" s="20"/>
       <c r="E112" s="4"/>
     </row>
-    <row r="113" spans="2:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="2:6" ht="14.45" customHeight="1">
       <c r="B113" s="2">
         <v>46054</v>
       </c>
-      <c r="C113" s="18">
+      <c r="C113" s="19">
         <v>18002</v>
       </c>
-      <c r="D113" s="19"/>
+      <c r="D113" s="20"/>
       <c r="E113" s="4"/>
     </row>
-    <row r="114" spans="2:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="2:6" ht="14.45" customHeight="1">
       <c r="B114" s="2">
         <v>46082</v>
       </c>
-      <c r="C114" s="18">
+      <c r="C114" s="19">
         <v>20184</v>
       </c>
-      <c r="D114" s="19"/>
+      <c r="D114" s="20"/>
       <c r="E114" s="4"/>
     </row>
-    <row r="115" spans="2:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="2:6" ht="14.45" customHeight="1">
       <c r="B115" s="2">
         <v>46113</v>
       </c>
-      <c r="C115" s="18"/>
-      <c r="D115" s="19"/>
+      <c r="C115" s="19">
+        <v>17928</v>
+      </c>
+      <c r="D115" s="20"/>
       <c r="E115" s="4"/>
     </row>
-    <row r="116" spans="2:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="2:6" ht="14.45" customHeight="1">
       <c r="B116" s="2">
         <v>46143</v>
       </c>
-      <c r="C116" s="18"/>
-      <c r="D116" s="19"/>
+      <c r="C116" s="19"/>
+      <c r="D116" s="20"/>
       <c r="E116" s="4"/>
     </row>
-    <row r="117" spans="2:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="2:6" ht="14.45" customHeight="1">
       <c r="B117" s="2">
         <v>46174</v>
       </c>
-      <c r="C117" s="18"/>
-      <c r="D117" s="19"/>
+      <c r="C117" s="19"/>
+      <c r="D117" s="20"/>
       <c r="E117" s="4"/>
       <c r="F117" s="4">
         <f>SUM(C112:D123)</f>
-        <v>56250</v>
-      </c>
-    </row>
-    <row r="118" spans="2:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+        <v>74178</v>
+      </c>
+    </row>
+    <row r="118" spans="2:6" ht="14.45" customHeight="1">
       <c r="B118" s="2">
         <v>46204</v>
       </c>
-      <c r="C118" s="18"/>
-      <c r="D118" s="19"/>
+      <c r="C118" s="19"/>
+      <c r="D118" s="20"/>
       <c r="E118" s="4"/>
     </row>
-    <row r="119" spans="2:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="2:6" ht="14.45" customHeight="1">
       <c r="B119" s="2">
         <v>46235</v>
       </c>
-      <c r="C119" s="18"/>
-      <c r="D119" s="19"/>
+      <c r="C119" s="19"/>
+      <c r="D119" s="20"/>
       <c r="E119" s="4"/>
     </row>
-    <row r="120" spans="2:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="2:6" ht="14.45" customHeight="1">
       <c r="B120" s="2">
         <v>46266</v>
       </c>
-      <c r="C120" s="18"/>
-      <c r="D120" s="19"/>
+      <c r="C120" s="19"/>
+      <c r="D120" s="20"/>
       <c r="E120" s="4"/>
     </row>
-    <row r="121" spans="2:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="2:6" ht="14.45" customHeight="1">
       <c r="B121" s="2">
         <v>46296</v>
       </c>
-      <c r="C121" s="18"/>
-      <c r="D121" s="19"/>
+      <c r="C121" s="19"/>
+      <c r="D121" s="20"/>
       <c r="E121" s="4"/>
     </row>
-    <row r="122" spans="2:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="2:6" ht="14.45" customHeight="1">
       <c r="B122" s="2">
         <v>46327</v>
       </c>
-      <c r="C122" s="18"/>
-      <c r="D122" s="19"/>
-    </row>
-    <row r="123" spans="2:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C122" s="19"/>
+      <c r="D122" s="20"/>
+    </row>
+    <row r="123" spans="2:6" ht="14.45" customHeight="1">
       <c r="B123" s="2">
         <v>46357</v>
       </c>
-      <c r="C123" s="18"/>
-      <c r="D123" s="19"/>
-    </row>
-    <row r="124" spans="2:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C123" s="19"/>
+      <c r="D123" s="20"/>
+    </row>
+    <row r="124" spans="2:6" ht="14.45" customHeight="1">
       <c r="B124" s="9"/>
       <c r="C124" s="5"/>
       <c r="D124" s="5"/>
     </row>
-    <row r="125" spans="2:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="2:6" ht="14.45" customHeight="1">
       <c r="B125" s="9"/>
       <c r="C125" s="5"/>
       <c r="D125" s="5"/>
     </row>
-    <row r="126" spans="2:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="2:6" ht="14.45" customHeight="1">
       <c r="B126" s="9"/>
       <c r="C126" s="5"/>
       <c r="D126" s="5"/>
     </row>
-    <row r="127" spans="2:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B127" s="15" t="s">
+    <row r="127" spans="2:6" ht="14.45" customHeight="1">
+      <c r="B127" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="C127" s="16"/>
-      <c r="D127" s="17"/>
-    </row>
-    <row r="128" spans="2:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C127" s="22"/>
+      <c r="D127" s="23"/>
+    </row>
+    <row r="128" spans="2:6" ht="14.45" customHeight="1">
       <c r="B128" s="2">
         <v>46023</v>
       </c>
-      <c r="C128" s="18">
+      <c r="C128" s="19">
         <v>30040.16</v>
       </c>
-      <c r="D128" s="19"/>
-    </row>
-    <row r="129" spans="2:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D128" s="20"/>
+    </row>
+    <row r="129" spans="2:6" ht="14.45" customHeight="1">
       <c r="B129" s="2">
         <v>46054</v>
       </c>
-      <c r="C129" s="18">
+      <c r="C129" s="19">
         <v>29778.37</v>
       </c>
-      <c r="D129" s="19"/>
-    </row>
-    <row r="130" spans="2:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D129" s="20"/>
+    </row>
+    <row r="130" spans="2:6" ht="14.45" customHeight="1">
       <c r="B130" s="2">
         <v>46082</v>
       </c>
-      <c r="C130" s="18">
+      <c r="C130" s="19">
         <v>36470.199999999997</v>
       </c>
-      <c r="D130" s="19"/>
+      <c r="D130" s="20"/>
       <c r="F130" s="4">
         <f>SUM(C128:D139)</f>
-        <v>96288.73</v>
-      </c>
-    </row>
-    <row r="131" spans="2:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+        <v>135758.22999999998</v>
+      </c>
+    </row>
+    <row r="131" spans="2:6" ht="14.45" customHeight="1">
       <c r="B131" s="2">
         <v>46113</v>
       </c>
-      <c r="C131" s="18"/>
-      <c r="D131" s="19"/>
-    </row>
-    <row r="132" spans="2:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C131" s="19">
+        <v>39469.5</v>
+      </c>
+      <c r="D131" s="20"/>
+    </row>
+    <row r="132" spans="2:6" ht="14.45" customHeight="1">
       <c r="B132" s="2">
         <v>46143</v>
       </c>
-      <c r="C132" s="18"/>
-      <c r="D132" s="19"/>
-    </row>
-    <row r="133" spans="2:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C132" s="19"/>
+      <c r="D132" s="20"/>
+    </row>
+    <row r="133" spans="2:6" ht="14.45" customHeight="1">
       <c r="B133" s="2">
         <v>46174</v>
       </c>
-      <c r="C133" s="18"/>
-      <c r="D133" s="19"/>
-    </row>
-    <row r="134" spans="2:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C133" s="19"/>
+      <c r="D133" s="20"/>
+    </row>
+    <row r="134" spans="2:6" ht="14.45" customHeight="1">
       <c r="B134" s="2">
         <v>46204</v>
       </c>
-      <c r="C134" s="18"/>
-      <c r="D134" s="19"/>
-    </row>
-    <row r="135" spans="2:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C134" s="19"/>
+      <c r="D134" s="20"/>
+    </row>
+    <row r="135" spans="2:6" ht="14.45" customHeight="1">
       <c r="B135" s="2">
         <v>46235</v>
       </c>
-      <c r="C135" s="18"/>
-      <c r="D135" s="19"/>
-    </row>
-    <row r="136" spans="2:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C135" s="19"/>
+      <c r="D135" s="20"/>
+    </row>
+    <row r="136" spans="2:6" ht="14.45" customHeight="1">
       <c r="B136" s="2">
         <v>46266</v>
       </c>
-      <c r="C136" s="18"/>
-      <c r="D136" s="19"/>
-    </row>
-    <row r="137" spans="2:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C136" s="19"/>
+      <c r="D136" s="20"/>
+    </row>
+    <row r="137" spans="2:6" ht="14.45" customHeight="1">
       <c r="B137" s="2">
         <v>46296</v>
       </c>
-      <c r="C137" s="18"/>
-      <c r="D137" s="19"/>
-    </row>
-    <row r="138" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C137" s="19"/>
+      <c r="D137" s="20"/>
+    </row>
+    <row r="138" spans="2:6" ht="14.45">
       <c r="B138" s="2">
         <v>46327</v>
       </c>
-      <c r="C138" s="18"/>
-      <c r="D138" s="19"/>
-    </row>
-    <row r="139" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C138" s="19"/>
+      <c r="D138" s="20"/>
+    </row>
+    <row r="139" spans="2:6" ht="14.45">
       <c r="B139" s="2">
         <v>46357</v>
       </c>
-      <c r="C139" s="18"/>
-      <c r="D139" s="19"/>
-    </row>
-    <row r="140" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C139" s="19"/>
+      <c r="D139" s="20"/>
+    </row>
+    <row r="140" spans="2:6" ht="14.45">
       <c r="B140" s="9"/>
       <c r="C140" s="5"/>
       <c r="D140" s="5"/>
     </row>
-    <row r="141" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="141" spans="2:6" ht="14.45">
       <c r="B141" s="9"/>
       <c r="C141" s="5"/>
       <c r="D141" s="5"/>
     </row>
-    <row r="142" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="142" spans="2:6" ht="14.45">
       <c r="B142" s="9"/>
       <c r="C142" s="5"/>
       <c r="D142" s="5"/>
     </row>
-    <row r="143" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B143" s="15" t="s">
+    <row r="143" spans="2:6" ht="14.45">
+      <c r="B143" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="C143" s="16"/>
-      <c r="D143" s="17"/>
-    </row>
-    <row r="144" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C143" s="22"/>
+      <c r="D143" s="23"/>
+    </row>
+    <row r="144" spans="2:6" ht="14.45">
       <c r="B144" s="2">
         <v>46023</v>
       </c>
-      <c r="C144" s="18"/>
-      <c r="D144" s="19"/>
-    </row>
-    <row r="145" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C144" s="19"/>
+      <c r="D144" s="20"/>
+    </row>
+    <row r="145" spans="2:6" ht="14.45">
       <c r="B145" s="2">
         <v>46054</v>
       </c>
-      <c r="C145" s="18"/>
-      <c r="D145" s="19"/>
-    </row>
-    <row r="146" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C145" s="19">
+        <v>167</v>
+      </c>
+      <c r="D145" s="20"/>
+    </row>
+    <row r="146" spans="2:6" ht="14.45">
       <c r="B146" s="2">
         <v>46082</v>
       </c>
-      <c r="C146" s="18"/>
-      <c r="D146" s="19"/>
-    </row>
-    <row r="147" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C146" s="19">
+        <v>5053</v>
+      </c>
+      <c r="D146" s="20"/>
+      <c r="E146" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="147" spans="2:6" ht="14.45">
       <c r="B147" s="2">
         <v>46113</v>
       </c>
-      <c r="C147" s="18"/>
-      <c r="D147" s="19"/>
-    </row>
-    <row r="148" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C147" s="19">
+        <v>100</v>
+      </c>
+      <c r="D147" s="20"/>
+    </row>
+    <row r="148" spans="2:6" ht="14.45">
       <c r="B148" s="2">
         <v>46143</v>
       </c>
-      <c r="C148" s="18"/>
-      <c r="D148" s="19"/>
-    </row>
-    <row r="149" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C148" s="19"/>
+      <c r="D148" s="20"/>
+    </row>
+    <row r="149" spans="2:6" ht="14.45">
       <c r="B149" s="2">
         <v>46174</v>
       </c>
-      <c r="C149" s="18"/>
-      <c r="D149" s="19"/>
+      <c r="C149" s="19"/>
+      <c r="D149" s="20"/>
       <c r="F149" s="4">
         <f>SUM(C144:D155)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="150" spans="2:6" x14ac:dyDescent="0.25">
+        <v>5320</v>
+      </c>
+    </row>
+    <row r="150" spans="2:6" ht="14.45">
       <c r="B150" s="2">
         <v>46204</v>
       </c>
-      <c r="C150" s="18"/>
-      <c r="D150" s="19"/>
-    </row>
-    <row r="151" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C150" s="19"/>
+      <c r="D150" s="20"/>
+    </row>
+    <row r="151" spans="2:6" ht="14.45">
       <c r="B151" s="2">
         <v>46235</v>
       </c>
-      <c r="C151" s="18"/>
-      <c r="D151" s="19"/>
-    </row>
-    <row r="152" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C151" s="19"/>
+      <c r="D151" s="20"/>
+    </row>
+    <row r="152" spans="2:6" ht="14.45">
       <c r="B152" s="2">
         <v>46266</v>
       </c>
-      <c r="C152" s="18"/>
-      <c r="D152" s="19"/>
-    </row>
-    <row r="153" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C152" s="19"/>
+      <c r="D152" s="20"/>
+    </row>
+    <row r="153" spans="2:6" ht="14.45">
       <c r="B153" s="2">
         <v>46296</v>
       </c>
-      <c r="C153" s="18"/>
-      <c r="D153" s="19"/>
-    </row>
-    <row r="154" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C153" s="19"/>
+      <c r="D153" s="20"/>
+    </row>
+    <row r="154" spans="2:6" ht="14.45">
       <c r="B154" s="2">
         <v>46327</v>
       </c>
-      <c r="C154" s="18"/>
-      <c r="D154" s="19"/>
-    </row>
-    <row r="155" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C154" s="19"/>
+      <c r="D154" s="20"/>
+    </row>
+    <row r="155" spans="2:6" ht="14.45">
       <c r="B155" s="2">
         <v>46357</v>
       </c>
-      <c r="C155" s="18"/>
-      <c r="D155" s="19"/>
-    </row>
-    <row r="162" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C155" s="19"/>
+      <c r="D155" s="20"/>
+    </row>
+    <row r="162" spans="2:4" ht="14.45">
       <c r="B162" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C162" s="21">
+        <v>20</v>
+      </c>
+      <c r="C162" s="28">
         <f>SUM(F9+F22+F37+F52+F67+F82+F97+F117+F130+F149+J107+O107)</f>
-        <v>832892.42999999993</v>
-      </c>
-      <c r="D162" s="22"/>
+        <v>1091515.6200000001</v>
+      </c>
+      <c r="D162" s="29"/>
     </row>
   </sheetData>
   <mergeCells count="174">
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="C38:D38"/>
-    <mergeCell ref="C39:D39"/>
-    <mergeCell ref="C40:D40"/>
-    <mergeCell ref="C41:D41"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="I79:K79"/>
+    <mergeCell ref="J80:K80"/>
+    <mergeCell ref="J81:K81"/>
+    <mergeCell ref="J82:K82"/>
+    <mergeCell ref="J83:K83"/>
+    <mergeCell ref="J84:K84"/>
+    <mergeCell ref="J85:K85"/>
+    <mergeCell ref="C69:D69"/>
+    <mergeCell ref="C68:D68"/>
+    <mergeCell ref="C76:D76"/>
+    <mergeCell ref="B79:D79"/>
+    <mergeCell ref="C80:D80"/>
+    <mergeCell ref="C81:D81"/>
+    <mergeCell ref="C82:D82"/>
+    <mergeCell ref="C83:D83"/>
+    <mergeCell ref="C70:D70"/>
+    <mergeCell ref="C71:D71"/>
+    <mergeCell ref="C72:D72"/>
+    <mergeCell ref="C73:D73"/>
+    <mergeCell ref="C74:D74"/>
+    <mergeCell ref="C75:D75"/>
+    <mergeCell ref="C155:D155"/>
+    <mergeCell ref="C162:D162"/>
+    <mergeCell ref="C149:D149"/>
+    <mergeCell ref="C150:D150"/>
+    <mergeCell ref="C151:D151"/>
+    <mergeCell ref="C152:D152"/>
+    <mergeCell ref="C153:D153"/>
+    <mergeCell ref="C154:D154"/>
+    <mergeCell ref="B143:D143"/>
+    <mergeCell ref="C144:D144"/>
+    <mergeCell ref="C145:D145"/>
+    <mergeCell ref="C146:D146"/>
+    <mergeCell ref="C147:D147"/>
+    <mergeCell ref="C148:D148"/>
+    <mergeCell ref="C134:D134"/>
+    <mergeCell ref="C135:D135"/>
+    <mergeCell ref="C136:D136"/>
+    <mergeCell ref="C137:D137"/>
+    <mergeCell ref="C138:D138"/>
+    <mergeCell ref="C139:D139"/>
+    <mergeCell ref="C128:D128"/>
+    <mergeCell ref="C129:D129"/>
+    <mergeCell ref="C130:D130"/>
+    <mergeCell ref="C131:D131"/>
+    <mergeCell ref="C132:D132"/>
+    <mergeCell ref="C133:D133"/>
+    <mergeCell ref="C119:D119"/>
+    <mergeCell ref="C120:D120"/>
+    <mergeCell ref="C121:D121"/>
+    <mergeCell ref="C122:D122"/>
+    <mergeCell ref="C123:D123"/>
+    <mergeCell ref="B127:D127"/>
+    <mergeCell ref="C113:D113"/>
+    <mergeCell ref="C114:D114"/>
+    <mergeCell ref="C115:D115"/>
+    <mergeCell ref="C116:D116"/>
+    <mergeCell ref="C117:D117"/>
+    <mergeCell ref="C118:D118"/>
+    <mergeCell ref="C106:D106"/>
+    <mergeCell ref="J106:K106"/>
+    <mergeCell ref="O106:P106"/>
+    <mergeCell ref="J107:K107"/>
+    <mergeCell ref="B111:D111"/>
+    <mergeCell ref="C112:D112"/>
+    <mergeCell ref="C104:D104"/>
+    <mergeCell ref="J104:K104"/>
+    <mergeCell ref="O104:P104"/>
+    <mergeCell ref="C105:D105"/>
+    <mergeCell ref="J105:K105"/>
+    <mergeCell ref="O105:P105"/>
+    <mergeCell ref="C102:D102"/>
+    <mergeCell ref="J102:K102"/>
+    <mergeCell ref="O102:P102"/>
+    <mergeCell ref="C103:D103"/>
+    <mergeCell ref="J103:K103"/>
+    <mergeCell ref="O103:P103"/>
+    <mergeCell ref="C100:D100"/>
+    <mergeCell ref="J100:K100"/>
+    <mergeCell ref="O100:P100"/>
+    <mergeCell ref="C101:D101"/>
+    <mergeCell ref="J101:K101"/>
+    <mergeCell ref="O101:P101"/>
+    <mergeCell ref="C98:D98"/>
+    <mergeCell ref="J98:K98"/>
+    <mergeCell ref="O98:P98"/>
+    <mergeCell ref="C99:D99"/>
+    <mergeCell ref="J99:K99"/>
+    <mergeCell ref="O99:P99"/>
+    <mergeCell ref="C96:D96"/>
+    <mergeCell ref="J96:K96"/>
+    <mergeCell ref="O96:P96"/>
+    <mergeCell ref="C97:D97"/>
+    <mergeCell ref="J97:K97"/>
+    <mergeCell ref="O97:P97"/>
+    <mergeCell ref="C90:D90"/>
+    <mergeCell ref="C91:D91"/>
+    <mergeCell ref="B94:D94"/>
+    <mergeCell ref="I94:K94"/>
+    <mergeCell ref="N94:P94"/>
+    <mergeCell ref="C95:D95"/>
+    <mergeCell ref="J95:K95"/>
+    <mergeCell ref="O95:P95"/>
+    <mergeCell ref="C84:D84"/>
+    <mergeCell ref="C85:D85"/>
+    <mergeCell ref="C86:D86"/>
+    <mergeCell ref="C87:D87"/>
+    <mergeCell ref="C88:D88"/>
+    <mergeCell ref="C89:D89"/>
+    <mergeCell ref="J86:K86"/>
+    <mergeCell ref="J87:K87"/>
+    <mergeCell ref="J88:K88"/>
+    <mergeCell ref="J89:K89"/>
+    <mergeCell ref="J90:K90"/>
+    <mergeCell ref="J91:K91"/>
+    <mergeCell ref="J92:K92"/>
     <mergeCell ref="C67:D67"/>
     <mergeCell ref="C66:D66"/>
     <mergeCell ref="C65:D65"/>
@@ -2367,122 +2479,42 @@
     <mergeCell ref="C55:D55"/>
     <mergeCell ref="C57:D57"/>
     <mergeCell ref="C56:D56"/>
-    <mergeCell ref="C90:D90"/>
-    <mergeCell ref="C91:D91"/>
-    <mergeCell ref="B94:D94"/>
-    <mergeCell ref="I94:K94"/>
-    <mergeCell ref="N94:P94"/>
-    <mergeCell ref="C95:D95"/>
-    <mergeCell ref="J95:K95"/>
-    <mergeCell ref="O95:P95"/>
-    <mergeCell ref="C84:D84"/>
-    <mergeCell ref="C85:D85"/>
-    <mergeCell ref="C86:D86"/>
-    <mergeCell ref="C87:D87"/>
-    <mergeCell ref="C88:D88"/>
-    <mergeCell ref="C89:D89"/>
-    <mergeCell ref="J86:K86"/>
-    <mergeCell ref="J87:K87"/>
-    <mergeCell ref="J88:K88"/>
-    <mergeCell ref="J89:K89"/>
-    <mergeCell ref="J90:K90"/>
-    <mergeCell ref="J91:K91"/>
-    <mergeCell ref="J92:K92"/>
-    <mergeCell ref="C98:D98"/>
-    <mergeCell ref="J98:K98"/>
-    <mergeCell ref="O98:P98"/>
-    <mergeCell ref="C99:D99"/>
-    <mergeCell ref="J99:K99"/>
-    <mergeCell ref="O99:P99"/>
-    <mergeCell ref="C96:D96"/>
-    <mergeCell ref="J96:K96"/>
-    <mergeCell ref="O96:P96"/>
-    <mergeCell ref="C97:D97"/>
-    <mergeCell ref="J97:K97"/>
-    <mergeCell ref="O97:P97"/>
-    <mergeCell ref="C102:D102"/>
-    <mergeCell ref="J102:K102"/>
-    <mergeCell ref="O102:P102"/>
-    <mergeCell ref="C103:D103"/>
-    <mergeCell ref="J103:K103"/>
-    <mergeCell ref="O103:P103"/>
-    <mergeCell ref="C100:D100"/>
-    <mergeCell ref="J100:K100"/>
-    <mergeCell ref="O100:P100"/>
-    <mergeCell ref="C101:D101"/>
-    <mergeCell ref="J101:K101"/>
-    <mergeCell ref="O101:P101"/>
-    <mergeCell ref="C106:D106"/>
-    <mergeCell ref="J106:K106"/>
-    <mergeCell ref="O106:P106"/>
-    <mergeCell ref="J107:K107"/>
-    <mergeCell ref="B111:D111"/>
-    <mergeCell ref="C112:D112"/>
-    <mergeCell ref="C104:D104"/>
-    <mergeCell ref="J104:K104"/>
-    <mergeCell ref="O104:P104"/>
-    <mergeCell ref="C105:D105"/>
-    <mergeCell ref="J105:K105"/>
-    <mergeCell ref="O105:P105"/>
-    <mergeCell ref="C119:D119"/>
-    <mergeCell ref="C120:D120"/>
-    <mergeCell ref="C121:D121"/>
-    <mergeCell ref="C122:D122"/>
-    <mergeCell ref="C123:D123"/>
-    <mergeCell ref="B127:D127"/>
-    <mergeCell ref="C113:D113"/>
-    <mergeCell ref="C114:D114"/>
-    <mergeCell ref="C115:D115"/>
-    <mergeCell ref="C116:D116"/>
-    <mergeCell ref="C117:D117"/>
-    <mergeCell ref="C118:D118"/>
-    <mergeCell ref="C134:D134"/>
-    <mergeCell ref="C135:D135"/>
-    <mergeCell ref="C136:D136"/>
-    <mergeCell ref="C137:D137"/>
-    <mergeCell ref="C138:D138"/>
-    <mergeCell ref="C139:D139"/>
-    <mergeCell ref="C128:D128"/>
-    <mergeCell ref="C129:D129"/>
-    <mergeCell ref="C130:D130"/>
-    <mergeCell ref="C131:D131"/>
-    <mergeCell ref="C132:D132"/>
-    <mergeCell ref="C133:D133"/>
-    <mergeCell ref="C155:D155"/>
-    <mergeCell ref="C162:D162"/>
-    <mergeCell ref="C149:D149"/>
-    <mergeCell ref="C150:D150"/>
-    <mergeCell ref="C151:D151"/>
-    <mergeCell ref="C152:D152"/>
-    <mergeCell ref="C153:D153"/>
-    <mergeCell ref="C154:D154"/>
-    <mergeCell ref="B143:D143"/>
-    <mergeCell ref="C144:D144"/>
-    <mergeCell ref="C145:D145"/>
-    <mergeCell ref="C146:D146"/>
-    <mergeCell ref="C147:D147"/>
-    <mergeCell ref="C148:D148"/>
-    <mergeCell ref="I79:K79"/>
-    <mergeCell ref="J80:K80"/>
-    <mergeCell ref="J81:K81"/>
-    <mergeCell ref="J82:K82"/>
-    <mergeCell ref="J83:K83"/>
-    <mergeCell ref="J84:K84"/>
-    <mergeCell ref="J85:K85"/>
-    <mergeCell ref="C69:D69"/>
-    <mergeCell ref="C68:D68"/>
-    <mergeCell ref="C76:D76"/>
-    <mergeCell ref="B79:D79"/>
-    <mergeCell ref="C80:D80"/>
-    <mergeCell ref="C81:D81"/>
-    <mergeCell ref="C82:D82"/>
-    <mergeCell ref="C83:D83"/>
-    <mergeCell ref="C70:D70"/>
-    <mergeCell ref="C71:D71"/>
-    <mergeCell ref="C72:D72"/>
-    <mergeCell ref="C73:D73"/>
-    <mergeCell ref="C74:D74"/>
-    <mergeCell ref="C75:D75"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="C40:D40"/>
+    <mergeCell ref="C41:D41"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C13:D13"/>
   </mergeCells>
   <conditionalFormatting sqref="B18">
     <cfRule type="uniqueValues" dxfId="1" priority="1"/>
@@ -2494,7 +2526,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3203085-85C2-4E3C-98FD-01CE94F157A9}">
   <dimension ref="B2:W162"/>
-  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="2" max="2" width="15.5703125" customWidth="1"/>
     <col min="3" max="3" width="10.28515625" customWidth="1"/>
@@ -2515,15 +2547,15 @@
     <col min="23" max="23" width="13.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:23" x14ac:dyDescent="0.25">
-      <c r="B2" s="26" t="s">
+    <row r="2" spans="2:23" ht="14.45">
+      <c r="B2" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
       <c r="E2" s="3"/>
     </row>
-    <row r="3" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:23" ht="14.45">
       <c r="B3" s="1"/>
       <c r="C3" s="30" t="s">
         <v>1</v>
@@ -2544,13 +2576,13 @@
       <c r="V3" s="7"/>
       <c r="W3" s="8"/>
     </row>
-    <row r="4" spans="2:23" x14ac:dyDescent="0.25">
-      <c r="B4" s="29" t="s">
+    <row r="4" spans="2:23" ht="14.45">
+      <c r="B4" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="29"/>
-      <c r="D4" s="29"/>
-      <c r="E4" s="29"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
       <c r="K4" s="7"/>
       <c r="L4" s="7"/>
       <c r="M4" s="7"/>
@@ -2565,14 +2597,14 @@
       <c r="V4" s="7"/>
       <c r="W4" s="8"/>
     </row>
-    <row r="5" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:23" ht="14.45">
       <c r="B5" s="2">
         <v>45658</v>
       </c>
-      <c r="C5" s="20">
+      <c r="C5" s="25">
         <v>41430</v>
       </c>
-      <c r="D5" s="29"/>
+      <c r="D5" s="18"/>
       <c r="E5" s="10"/>
       <c r="K5" s="10"/>
       <c r="L5" s="10"/>
@@ -2588,58 +2620,58 @@
       <c r="V5" s="10"/>
       <c r="W5" s="10"/>
     </row>
-    <row r="6" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:23" ht="14.45">
       <c r="B6" s="2">
         <v>45689</v>
       </c>
-      <c r="C6" s="20">
+      <c r="C6" s="25">
         <v>41430</v>
       </c>
-      <c r="D6" s="29"/>
+      <c r="D6" s="18"/>
       <c r="E6" s="10"/>
     </row>
-    <row r="7" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:23" ht="14.45">
       <c r="B7" s="2">
         <v>45717</v>
       </c>
-      <c r="C7" s="20">
+      <c r="C7" s="25">
         <v>41430</v>
       </c>
-      <c r="D7" s="29"/>
+      <c r="D7" s="18"/>
       <c r="E7" s="10"/>
     </row>
-    <row r="8" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:23" ht="14.45">
       <c r="B8" s="2">
         <v>45748</v>
       </c>
-      <c r="C8" s="20">
+      <c r="C8" s="25">
         <v>41430</v>
       </c>
-      <c r="D8" s="29"/>
+      <c r="D8" s="18"/>
       <c r="E8" s="10"/>
     </row>
-    <row r="9" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:23" ht="14.45">
       <c r="B9" s="2">
         <v>45778</v>
       </c>
-      <c r="C9" s="20">
+      <c r="C9" s="25">
         <v>41430</v>
       </c>
-      <c r="D9" s="29"/>
+      <c r="D9" s="18"/>
       <c r="E9" s="10"/>
       <c r="F9" s="4">
         <f>SUM(C5:D16)</f>
         <v>522515.62299999996</v>
       </c>
     </row>
-    <row r="10" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:23" ht="14.45">
       <c r="B10" s="2">
         <v>45809</v>
       </c>
-      <c r="C10" s="20">
+      <c r="C10" s="25">
         <v>44010</v>
       </c>
-      <c r="D10" s="29"/>
+      <c r="D10" s="18"/>
       <c r="E10" s="10"/>
       <c r="J10" t="s">
         <v>3</v>
@@ -2651,14 +2683,14 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:23" ht="14.45">
       <c r="B11" s="2">
         <v>45839</v>
       </c>
-      <c r="C11" s="20">
+      <c r="C11" s="25">
         <v>44936.99</v>
       </c>
-      <c r="D11" s="29"/>
+      <c r="D11" s="18"/>
       <c r="E11" s="10"/>
       <c r="I11" s="9">
         <v>45658</v>
@@ -2679,14 +2711,14 @@
         <v>833.25221238938047</v>
       </c>
     </row>
-    <row r="12" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:23" ht="14.45">
       <c r="B12" s="2">
         <v>45870</v>
       </c>
-      <c r="C12" s="20">
+      <c r="C12" s="25">
         <v>44930</v>
       </c>
-      <c r="D12" s="29"/>
+      <c r="D12" s="18"/>
       <c r="E12" s="10"/>
       <c r="I12" s="9">
         <v>45689</v>
@@ -2700,14 +2732,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:23" ht="14.45">
       <c r="B13" s="2">
         <v>45901</v>
       </c>
-      <c r="C13" s="20">
+      <c r="C13" s="25">
         <v>45015.642999999996</v>
       </c>
-      <c r="D13" s="29"/>
+      <c r="D13" s="18"/>
       <c r="E13" s="10"/>
       <c r="I13" s="9">
         <v>45717</v>
@@ -2721,14 +2753,14 @@
         <v>55400</v>
       </c>
     </row>
-    <row r="14" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:23" ht="14.45">
       <c r="B14" s="2">
         <v>45931</v>
       </c>
-      <c r="C14" s="20">
+      <c r="C14" s="25">
         <v>45159.46</v>
       </c>
-      <c r="D14" s="29"/>
+      <c r="D14" s="18"/>
       <c r="E14" s="10"/>
       <c r="I14" s="9">
         <v>45748</v>
@@ -2742,14 +2774,14 @@
         <v>48000</v>
       </c>
     </row>
-    <row r="15" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:23" ht="14.45">
       <c r="B15" s="2">
         <v>45962</v>
       </c>
-      <c r="C15" s="20">
+      <c r="C15" s="25">
         <v>45160.800000000003</v>
       </c>
-      <c r="D15" s="29"/>
+      <c r="D15" s="18"/>
       <c r="E15" s="10"/>
       <c r="I15" s="9">
         <v>45778</v>
@@ -2763,14 +2795,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:23" ht="14.45">
       <c r="B16" s="2">
         <v>45992</v>
       </c>
-      <c r="C16" s="20">
+      <c r="C16" s="25">
         <v>46152.73</v>
       </c>
-      <c r="D16" s="29"/>
+      <c r="D16" s="18"/>
       <c r="E16" s="10"/>
       <c r="I16" s="9">
         <v>45809</v>
@@ -2784,7 +2816,7 @@
         <v>48000</v>
       </c>
     </row>
-    <row r="17" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:11" ht="14.45">
       <c r="B17" s="9"/>
       <c r="C17" s="5"/>
       <c r="D17" s="6"/>
@@ -2801,7 +2833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:11" ht="14.45">
       <c r="I18" s="9">
         <v>45870</v>
       </c>
@@ -2814,12 +2846,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B19" s="15" t="s">
+    <row r="19" spans="2:11" ht="14.45">
+      <c r="B19" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="C19" s="16"/>
-      <c r="D19" s="17"/>
+      <c r="C19" s="22"/>
+      <c r="D19" s="23"/>
       <c r="I19" s="9">
         <v>45901</v>
       </c>
@@ -2832,15 +2864,15 @@
         <v>48000</v>
       </c>
     </row>
-    <row r="20" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:11" ht="14.45">
       <c r="B20" s="2">
         <v>45658</v>
       </c>
-      <c r="C20" s="18">
+      <c r="C20" s="19">
         <f>11949.03+1459.08+319.39</f>
         <v>13727.5</v>
       </c>
-      <c r="D20" s="25"/>
+      <c r="D20" s="24"/>
       <c r="I20" s="9">
         <v>45931</v>
       </c>
@@ -2853,15 +2885,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:11" ht="14.45">
       <c r="B21" s="2">
         <v>45689</v>
       </c>
-      <c r="C21" s="18">
+      <c r="C21" s="19">
         <f>14456.16+2124.54+1142.32+156.96</f>
         <v>17879.98</v>
       </c>
-      <c r="D21" s="25"/>
+      <c r="D21" s="24"/>
       <c r="I21" s="9">
         <v>45962</v>
       </c>
@@ -2874,15 +2906,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:11" ht="14.45">
       <c r="B22" s="2">
         <v>45717</v>
       </c>
-      <c r="C22" s="18">
+      <c r="C22" s="19">
         <f>15660.94+895.86+1429.98</f>
         <v>17986.78</v>
       </c>
-      <c r="D22" s="25"/>
+      <c r="D22" s="24"/>
       <c r="F22" s="4">
         <f>SUM(C20:D31)</f>
         <v>227049.24000000002</v>
@@ -2899,696 +2931,696 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:11" ht="14.45">
       <c r="B23" s="2">
         <v>45748</v>
       </c>
-      <c r="C23" s="18">
+      <c r="C23" s="19">
         <f>31632.79+899.52+1404.78+144.72</f>
         <v>34081.810000000005</v>
       </c>
-      <c r="D23" s="25"/>
+      <c r="D23" s="24"/>
       <c r="F23" s="4"/>
       <c r="I23" s="9"/>
     </row>
-    <row r="24" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:11" ht="14.45">
       <c r="B24" s="2">
         <v>45778</v>
       </c>
-      <c r="C24" s="18">
+      <c r="C24" s="19">
         <f>14482.01+1222.32+83.05</f>
         <v>15787.38</v>
       </c>
-      <c r="D24" s="25"/>
+      <c r="D24" s="24"/>
       <c r="F24" s="4"/>
       <c r="I24" s="9"/>
     </row>
-    <row r="25" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:11" ht="14.45">
       <c r="B25" s="2">
         <v>45809</v>
       </c>
-      <c r="C25" s="18">
+      <c r="C25" s="19">
         <f>16963.02+1765.44+749.18+291.51</f>
         <v>19769.149999999998</v>
       </c>
-      <c r="D25" s="25"/>
+      <c r="D25" s="24"/>
       <c r="F25" s="4"/>
     </row>
-    <row r="26" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:11" ht="14.45">
       <c r="B26" s="2">
         <v>45839</v>
       </c>
-      <c r="C26" s="18">
+      <c r="C26" s="19">
         <f>14276.19+2577.99+727.77+177.39</f>
         <v>17759.34</v>
       </c>
-      <c r="D26" s="25"/>
+      <c r="D26" s="24"/>
       <c r="F26" s="4"/>
     </row>
-    <row r="27" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:11" ht="14.45">
       <c r="B27" s="2">
         <v>45870</v>
       </c>
-      <c r="C27" s="18">
+      <c r="C27" s="19">
         <f>13844.26+812.17</f>
         <v>14656.43</v>
       </c>
-      <c r="D27" s="25"/>
+      <c r="D27" s="24"/>
       <c r="F27" s="4"/>
     </row>
-    <row r="28" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:11" ht="14.45">
       <c r="B28" s="2">
         <v>45901</v>
       </c>
-      <c r="C28" s="18">
+      <c r="C28" s="19">
         <f>11947.75+3241.73+981.58+61.64</f>
         <v>16232.699999999999</v>
       </c>
-      <c r="D28" s="25"/>
+      <c r="D28" s="24"/>
       <c r="F28" s="4"/>
     </row>
-    <row r="29" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:11" ht="14.45">
       <c r="B29" s="2">
         <v>45931</v>
       </c>
-      <c r="C29" s="18">
+      <c r="C29" s="19">
         <f>25663.46+1489.5+850.29+226.81</f>
         <v>28230.06</v>
       </c>
-      <c r="D29" s="25"/>
+      <c r="D29" s="24"/>
       <c r="F29" s="4"/>
     </row>
-    <row r="30" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:11" ht="14.45">
       <c r="B30" s="2">
         <v>45962</v>
       </c>
-      <c r="C30" s="18">
+      <c r="C30" s="19">
         <f>13224.12+950.42</f>
         <v>14174.54</v>
       </c>
-      <c r="D30" s="25"/>
+      <c r="D30" s="24"/>
       <c r="F30" s="4"/>
     </row>
-    <row r="31" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:11" ht="14.45">
       <c r="B31" s="2">
         <v>45992</v>
       </c>
-      <c r="C31" s="18">
+      <c r="C31" s="19">
         <v>16763.57</v>
       </c>
-      <c r="D31" s="25"/>
+      <c r="D31" s="24"/>
       <c r="F31" s="4"/>
     </row>
-    <row r="32" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:11" ht="14.45">
       <c r="B32" s="9"/>
       <c r="C32" s="5"/>
       <c r="D32" s="6"/>
       <c r="F32" s="4"/>
     </row>
-    <row r="34" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B34" s="15" t="s">
+    <row r="34" spans="2:9" ht="14.45">
+      <c r="B34" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="C34" s="16"/>
-      <c r="D34" s="17"/>
-    </row>
-    <row r="35" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="C34" s="22"/>
+      <c r="D34" s="23"/>
+    </row>
+    <row r="35" spans="2:9" ht="14.45">
       <c r="B35" s="2">
         <v>45658</v>
       </c>
-      <c r="C35" s="18">
+      <c r="C35" s="19">
         <f>12457.03+9.96+35</f>
         <v>12501.99</v>
       </c>
-      <c r="D35" s="25"/>
-    </row>
-    <row r="36" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="D35" s="24"/>
+    </row>
+    <row r="36" spans="2:9" ht="14.45">
       <c r="B36" s="2">
         <v>45689</v>
       </c>
-      <c r="C36" s="18">
+      <c r="C36" s="19">
         <f>11977.68+9.96+35</f>
         <v>12022.64</v>
       </c>
-      <c r="D36" s="25"/>
-    </row>
-    <row r="37" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="D36" s="24"/>
+    </row>
+    <row r="37" spans="2:9" ht="14.45">
       <c r="B37" s="2">
         <v>45717</v>
       </c>
-      <c r="C37" s="18">
+      <c r="C37" s="19">
         <f>11191.45+9.96+35</f>
         <v>11236.41</v>
       </c>
-      <c r="D37" s="25"/>
+      <c r="D37" s="24"/>
       <c r="F37" s="4">
         <f>SUM(C35:D46)</f>
         <v>119711.46999999997</v>
       </c>
     </row>
-    <row r="38" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:9" ht="14.45">
       <c r="B38" s="2">
         <v>45748</v>
       </c>
-      <c r="C38" s="18">
+      <c r="C38" s="19">
         <f>9172.56+9.96+35</f>
         <v>9217.5199999999986</v>
       </c>
-      <c r="D38" s="25"/>
+      <c r="D38" s="24"/>
       <c r="F38" s="4"/>
       <c r="I38" s="4"/>
     </row>
-    <row r="39" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:9" ht="14.45">
       <c r="B39" s="2">
         <v>45778</v>
       </c>
-      <c r="C39" s="18">
+      <c r="C39" s="19">
         <f>9654.35+9.96+35</f>
         <v>9699.31</v>
       </c>
-      <c r="D39" s="25"/>
+      <c r="D39" s="24"/>
       <c r="F39" s="4"/>
       <c r="I39" s="4"/>
     </row>
-    <row r="40" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:9" ht="14.45">
       <c r="B40" s="2">
         <v>45809</v>
       </c>
-      <c r="C40" s="18">
+      <c r="C40" s="19">
         <f>9150.55+9.96+35</f>
         <v>9195.5099999999984</v>
       </c>
-      <c r="D40" s="25"/>
+      <c r="D40" s="24"/>
       <c r="F40" s="4"/>
     </row>
-    <row r="41" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:9" ht="14.45">
       <c r="B41" s="2">
         <v>45839</v>
       </c>
-      <c r="C41" s="18">
+      <c r="C41" s="19">
         <f>9295.99+9.96+35</f>
         <v>9340.9499999999989</v>
       </c>
-      <c r="D41" s="25"/>
+      <c r="D41" s="24"/>
       <c r="F41" s="4"/>
     </row>
-    <row r="42" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:9" ht="14.45">
       <c r="B42" s="2">
         <v>45870</v>
       </c>
-      <c r="C42" s="18">
+      <c r="C42" s="19">
         <f>9150.55+9.96+35</f>
         <v>9195.5099999999984</v>
       </c>
-      <c r="D42" s="25"/>
+      <c r="D42" s="24"/>
       <c r="F42" s="4"/>
     </row>
-    <row r="43" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:9" ht="14.45">
       <c r="B43" s="2">
         <v>45901</v>
       </c>
-      <c r="C43" s="18">
+      <c r="C43" s="19">
         <f>9451.98+9.96+35</f>
         <v>9496.9399999999987</v>
       </c>
-      <c r="D43" s="25"/>
+      <c r="D43" s="24"/>
       <c r="F43" s="4"/>
     </row>
-    <row r="44" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:9" ht="14.45">
       <c r="B44" s="2">
         <v>45931</v>
       </c>
-      <c r="C44" s="18">
+      <c r="C44" s="19">
         <f>9251.22+9.96+35</f>
         <v>9296.1799999999985</v>
       </c>
-      <c r="D44" s="25"/>
+      <c r="D44" s="24"/>
       <c r="F44" s="4"/>
     </row>
-    <row r="45" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:9" ht="14.45">
       <c r="B45" s="2">
         <v>45962</v>
       </c>
-      <c r="C45" s="18">
+      <c r="C45" s="19">
         <f>9174.54+35+9.96</f>
         <v>9219.5</v>
       </c>
-      <c r="D45" s="25"/>
+      <c r="D45" s="24"/>
       <c r="F45" s="4"/>
     </row>
-    <row r="46" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:9" ht="14.45">
       <c r="B46" s="2">
         <v>45992</v>
       </c>
-      <c r="C46" s="18">
+      <c r="C46" s="19">
         <f>9244.05+9.96+35</f>
         <v>9289.0099999999984</v>
       </c>
-      <c r="D46" s="25"/>
+      <c r="D46" s="24"/>
       <c r="F46" s="4"/>
     </row>
-    <row r="47" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:9" ht="14.45">
       <c r="B47" s="9"/>
       <c r="C47" s="5"/>
       <c r="D47" s="6"/>
       <c r="F47" s="4"/>
     </row>
-    <row r="49" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B49" s="15" t="s">
+    <row r="49" spans="2:6" ht="14.45">
+      <c r="B49" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="C49" s="16"/>
-      <c r="D49" s="17"/>
-    </row>
-    <row r="50" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C49" s="22"/>
+      <c r="D49" s="23"/>
+    </row>
+    <row r="50" spans="2:6" ht="14.45">
       <c r="B50" s="2">
         <v>45658</v>
       </c>
-      <c r="C50" s="18">
+      <c r="C50" s="19">
         <v>52735.51</v>
       </c>
-      <c r="D50" s="19"/>
-    </row>
-    <row r="51" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="D50" s="20"/>
+    </row>
+    <row r="51" spans="2:6" ht="14.45">
       <c r="B51" s="2">
         <v>45689</v>
       </c>
-      <c r="C51" s="18">
+      <c r="C51" s="19">
         <v>47448.62</v>
       </c>
-      <c r="D51" s="19"/>
-    </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="D51" s="20"/>
+    </row>
+    <row r="52" spans="2:6" ht="14.45">
       <c r="B52" s="2">
         <v>45717</v>
       </c>
-      <c r="C52" s="18">
+      <c r="C52" s="19">
         <v>47448.62</v>
       </c>
-      <c r="D52" s="19"/>
+      <c r="D52" s="20"/>
       <c r="F52" s="4">
         <f>SUM(C50:D61)</f>
         <v>617587.11</v>
       </c>
     </row>
-    <row r="53" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:6" ht="14.45">
       <c r="B53" s="2">
         <v>45748</v>
       </c>
-      <c r="C53" s="18">
+      <c r="C53" s="19">
         <v>47448.62</v>
       </c>
-      <c r="D53" s="19"/>
+      <c r="D53" s="20"/>
       <c r="F53" s="4"/>
     </row>
-    <row r="54" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:6" ht="14.45">
       <c r="B54" s="2">
         <v>45778</v>
       </c>
-      <c r="C54" s="18">
+      <c r="C54" s="19">
         <v>49813.94</v>
       </c>
-      <c r="D54" s="19"/>
+      <c r="D54" s="20"/>
       <c r="F54" s="4"/>
     </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:6" ht="14.45">
       <c r="B55" s="2">
         <v>45809</v>
       </c>
-      <c r="C55" s="18">
+      <c r="C55" s="19">
         <v>50602.38</v>
       </c>
-      <c r="D55" s="19"/>
+      <c r="D55" s="20"/>
       <c r="F55" s="4"/>
     </row>
-    <row r="56" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:6" ht="14.45">
       <c r="B56" s="2">
         <v>45839</v>
       </c>
-      <c r="C56" s="18">
+      <c r="C56" s="19">
         <v>51390.82</v>
       </c>
-      <c r="D56" s="19"/>
+      <c r="D56" s="20"/>
       <c r="F56" s="4"/>
     </row>
-    <row r="57" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:6" ht="14.45">
       <c r="B57" s="2">
         <v>45870</v>
       </c>
-      <c r="C57" s="18">
+      <c r="C57" s="19">
         <v>52967.7</v>
       </c>
-      <c r="D57" s="19"/>
+      <c r="D57" s="20"/>
       <c r="F57" s="4"/>
     </row>
-    <row r="58" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:6" ht="14.45">
       <c r="B58" s="2">
         <v>45901</v>
       </c>
-      <c r="C58" s="18">
+      <c r="C58" s="19">
         <v>53738.63</v>
       </c>
-      <c r="D58" s="19"/>
+      <c r="D58" s="20"/>
       <c r="F58" s="4"/>
     </row>
-    <row r="59" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:6" ht="14.45">
       <c r="B59" s="2">
         <v>45931</v>
       </c>
-      <c r="C59" s="18">
+      <c r="C59" s="19">
         <v>53065.01</v>
       </c>
-      <c r="D59" s="19"/>
+      <c r="D59" s="20"/>
       <c r="F59" s="4"/>
     </row>
-    <row r="60" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:6" ht="14.45">
       <c r="B60" s="2">
         <v>45962</v>
       </c>
-      <c r="C60" s="18">
+      <c r="C60" s="19">
         <v>55463.63</v>
       </c>
-      <c r="D60" s="19"/>
+      <c r="D60" s="20"/>
       <c r="F60" s="4"/>
     </row>
-    <row r="61" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:6" ht="14.45">
       <c r="B61" s="2">
         <v>45992</v>
       </c>
-      <c r="C61" s="18">
+      <c r="C61" s="19">
         <v>55463.63</v>
       </c>
-      <c r="D61" s="19"/>
+      <c r="D61" s="20"/>
       <c r="F61" s="4"/>
     </row>
-    <row r="64" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B64" s="15" t="s">
+    <row r="64" spans="2:6" ht="14.45">
+      <c r="B64" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="C64" s="16"/>
-      <c r="D64" s="17"/>
-    </row>
-    <row r="65" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C64" s="22"/>
+      <c r="D64" s="23"/>
+    </row>
+    <row r="65" spans="2:6" ht="14.45">
       <c r="B65" s="2">
         <v>45658</v>
       </c>
-      <c r="C65" s="18">
+      <c r="C65" s="19">
         <v>9798.5300000000007</v>
       </c>
-      <c r="D65" s="25"/>
-    </row>
-    <row r="66" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="D65" s="24"/>
+    </row>
+    <row r="66" spans="2:6" ht="14.45">
       <c r="B66" s="2">
         <v>45689</v>
       </c>
-      <c r="C66" s="18">
+      <c r="C66" s="19">
         <v>10568.79</v>
       </c>
-      <c r="D66" s="25"/>
-    </row>
-    <row r="67" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="D66" s="24"/>
+    </row>
+    <row r="67" spans="2:6" ht="14.45">
       <c r="B67" s="2">
         <v>45717</v>
       </c>
-      <c r="C67" s="18">
+      <c r="C67" s="19">
         <v>10655.5</v>
       </c>
-      <c r="D67" s="19"/>
+      <c r="D67" s="20"/>
       <c r="F67" s="4">
         <f>SUM(C65:D76)</f>
         <v>117903.48</v>
       </c>
     </row>
-    <row r="68" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:6" ht="14.45">
       <c r="B68" s="2">
         <v>45748</v>
       </c>
-      <c r="C68" s="18">
+      <c r="C68" s="19">
         <v>10655.94</v>
       </c>
-      <c r="D68" s="19"/>
-    </row>
-    <row r="69" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="D68" s="20"/>
+    </row>
+    <row r="69" spans="2:6" ht="14.45">
       <c r="B69" s="2">
         <v>45778</v>
       </c>
-      <c r="C69" s="18">
+      <c r="C69" s="19">
         <v>11499.86</v>
       </c>
-      <c r="D69" s="19"/>
-    </row>
-    <row r="70" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="D69" s="20"/>
+    </row>
+    <row r="70" spans="2:6" ht="14.45">
       <c r="B70" s="2">
         <v>45809</v>
       </c>
-      <c r="C70" s="18">
+      <c r="C70" s="19">
         <v>10957.66</v>
       </c>
-      <c r="D70" s="19"/>
-    </row>
-    <row r="71" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="D70" s="20"/>
+    </row>
+    <row r="71" spans="2:6" ht="14.45">
       <c r="B71" s="2">
         <v>45839</v>
       </c>
-      <c r="C71" s="18">
+      <c r="C71" s="19">
         <v>11690.16</v>
       </c>
-      <c r="D71" s="19"/>
-    </row>
-    <row r="72" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="D71" s="20"/>
+    </row>
+    <row r="72" spans="2:6" ht="14.45">
       <c r="B72" s="2">
         <v>45870</v>
       </c>
-      <c r="C72" s="18">
+      <c r="C72" s="19">
         <v>10534.26</v>
       </c>
-      <c r="D72" s="19"/>
-    </row>
-    <row r="73" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="D72" s="20"/>
+    </row>
+    <row r="73" spans="2:6" ht="14.45">
       <c r="B73" s="2">
         <v>45901</v>
       </c>
-      <c r="C73" s="18">
+      <c r="C73" s="19">
         <v>7435.25</v>
       </c>
-      <c r="D73" s="19"/>
-    </row>
-    <row r="74" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="D73" s="20"/>
+    </row>
+    <row r="74" spans="2:6" ht="14.45">
       <c r="B74" s="2">
         <v>45931</v>
       </c>
-      <c r="C74" s="18">
+      <c r="C74" s="19">
         <v>9268.44</v>
       </c>
-      <c r="D74" s="19"/>
-    </row>
-    <row r="75" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="D74" s="20"/>
+    </row>
+    <row r="75" spans="2:6" ht="14.45">
       <c r="B75" s="2">
         <v>45962</v>
       </c>
-      <c r="C75" s="18">
+      <c r="C75" s="19">
         <v>6758.75</v>
       </c>
-      <c r="D75" s="19"/>
-    </row>
-    <row r="76" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="D75" s="20"/>
+    </row>
+    <row r="76" spans="2:6" ht="14.45">
       <c r="B76" s="2">
         <v>45992</v>
       </c>
-      <c r="C76" s="18">
+      <c r="C76" s="19">
         <v>8080.34</v>
       </c>
-      <c r="D76" s="19"/>
-    </row>
-    <row r="77" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="D76" s="20"/>
+    </row>
+    <row r="77" spans="2:6" ht="14.45">
       <c r="B77" s="9"/>
       <c r="C77" s="5"/>
       <c r="D77" s="5"/>
     </row>
-    <row r="78" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:6" ht="14.45">
       <c r="B78" s="9"/>
       <c r="C78" s="5"/>
       <c r="D78" s="5"/>
     </row>
-    <row r="79" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B79" s="15" t="s">
+    <row r="79" spans="2:6" ht="14.45">
+      <c r="B79" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="C79" s="16"/>
-      <c r="D79" s="17"/>
-    </row>
-    <row r="80" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C79" s="22"/>
+      <c r="D79" s="23"/>
+    </row>
+    <row r="80" spans="2:6" ht="14.45">
       <c r="B80" s="2">
         <v>45658</v>
       </c>
-      <c r="C80" s="18"/>
-      <c r="D80" s="25"/>
-    </row>
-    <row r="81" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="C80" s="19"/>
+      <c r="D80" s="24"/>
+    </row>
+    <row r="81" spans="2:16" ht="14.45">
       <c r="B81" s="2">
         <v>45689</v>
       </c>
-      <c r="C81" s="18"/>
-      <c r="D81" s="25"/>
-    </row>
-    <row r="82" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="C81" s="19"/>
+      <c r="D81" s="24"/>
+    </row>
+    <row r="82" spans="2:16" ht="14.45">
       <c r="B82" s="2">
         <v>45717</v>
       </c>
-      <c r="C82" s="18"/>
-      <c r="D82" s="19"/>
+      <c r="C82" s="19"/>
+      <c r="D82" s="20"/>
       <c r="F82" s="4">
         <f>SUM(C80:D91)</f>
         <v>56040</v>
       </c>
     </row>
-    <row r="83" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:16" ht="14.45">
       <c r="B83" s="2">
         <v>45748</v>
       </c>
-      <c r="C83" s="18"/>
-      <c r="D83" s="19"/>
-    </row>
-    <row r="84" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="C83" s="19"/>
+      <c r="D83" s="20"/>
+    </row>
+    <row r="84" spans="2:16" ht="14.45">
       <c r="B84" s="2">
         <v>45778</v>
       </c>
-      <c r="C84" s="18"/>
-      <c r="D84" s="19"/>
-    </row>
-    <row r="85" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="C84" s="19"/>
+      <c r="D84" s="20"/>
+    </row>
+    <row r="85" spans="2:16" ht="14.45">
       <c r="B85" s="2">
         <v>45809</v>
       </c>
-      <c r="C85" s="18"/>
-      <c r="D85" s="19"/>
-    </row>
-    <row r="86" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="C85" s="19"/>
+      <c r="D85" s="20"/>
+    </row>
+    <row r="86" spans="2:16" ht="14.45">
       <c r="B86" s="2">
         <v>45839</v>
       </c>
-      <c r="C86" s="18"/>
-      <c r="D86" s="19"/>
-    </row>
-    <row r="87" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="C86" s="19"/>
+      <c r="D86" s="20"/>
+    </row>
+    <row r="87" spans="2:16" ht="14.45">
       <c r="B87" s="2">
         <v>45870</v>
       </c>
-      <c r="C87" s="18"/>
-      <c r="D87" s="19"/>
+      <c r="C87" s="19"/>
+      <c r="D87" s="20"/>
       <c r="F87" s="4"/>
     </row>
-    <row r="88" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="88" spans="2:16" ht="14.45">
       <c r="B88" s="2">
         <v>45901</v>
       </c>
-      <c r="C88" s="18">
+      <c r="C88" s="19">
         <v>56040</v>
       </c>
-      <c r="D88" s="19"/>
-    </row>
-    <row r="89" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="D88" s="20"/>
+    </row>
+    <row r="89" spans="2:16" ht="14.45">
       <c r="B89" s="2">
         <v>45931</v>
       </c>
-      <c r="C89" s="18"/>
-      <c r="D89" s="19"/>
+      <c r="C89" s="19"/>
+      <c r="D89" s="20"/>
       <c r="G89" s="12">
         <v>22700</v>
       </c>
       <c r="H89" s="13"/>
     </row>
-    <row r="90" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="90" spans="2:16" ht="14.45">
       <c r="B90" s="2">
         <v>45962</v>
       </c>
-      <c r="C90" s="18"/>
-      <c r="D90" s="19"/>
-    </row>
-    <row r="91" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="C90" s="19"/>
+      <c r="D90" s="20"/>
+    </row>
+    <row r="91" spans="2:16" ht="14.45">
       <c r="B91" s="2">
         <v>45992</v>
       </c>
-      <c r="C91" s="18"/>
-      <c r="D91" s="19"/>
-    </row>
-    <row r="92" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C91" s="19"/>
+      <c r="D91" s="20"/>
+    </row>
+    <row r="92" spans="2:16" ht="15.75" customHeight="1">
       <c r="B92" s="9"/>
       <c r="C92" s="5"/>
       <c r="D92" s="5"/>
     </row>
-    <row r="93" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="2:16" ht="15.75" customHeight="1">
       <c r="B93" s="9"/>
       <c r="C93" s="5"/>
       <c r="D93" s="5"/>
     </row>
-    <row r="94" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B94" s="15" t="s">
+    <row r="94" spans="2:16" ht="15.75" customHeight="1">
+      <c r="B94" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="C94" s="16"/>
-      <c r="D94" s="17"/>
-      <c r="I94" s="15" t="s">
+      <c r="C94" s="22"/>
+      <c r="D94" s="23"/>
+      <c r="I94" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="J94" s="16"/>
-      <c r="K94" s="17"/>
-      <c r="N94" s="15" t="s">
+      <c r="J94" s="22"/>
+      <c r="K94" s="23"/>
+      <c r="N94" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="O94" s="16"/>
-      <c r="P94" s="17"/>
-    </row>
-    <row r="95" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O94" s="22"/>
+      <c r="P94" s="23"/>
+    </row>
+    <row r="95" spans="2:16" ht="15.75" customHeight="1">
       <c r="B95" s="2">
         <v>45658</v>
       </c>
-      <c r="C95" s="18">
+      <c r="C95" s="19">
         <v>21840</v>
       </c>
-      <c r="D95" s="25"/>
+      <c r="D95" s="24"/>
       <c r="I95" s="2">
         <v>45658</v>
       </c>
-      <c r="J95" s="18"/>
-      <c r="K95" s="19"/>
+      <c r="J95" s="19"/>
+      <c r="K95" s="20"/>
       <c r="N95" s="2">
         <v>45658</v>
       </c>
-      <c r="O95" s="18">
+      <c r="O95" s="19">
         <v>39000</v>
       </c>
-      <c r="P95" s="25"/>
-    </row>
-    <row r="96" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P95" s="24"/>
+    </row>
+    <row r="96" spans="2:16" ht="15.75" customHeight="1">
       <c r="B96" s="2">
         <v>45689</v>
       </c>
-      <c r="C96" s="18">
+      <c r="C96" s="19">
         <v>21840</v>
       </c>
-      <c r="D96" s="25"/>
+      <c r="D96" s="24"/>
       <c r="I96" s="2">
         <v>45689</v>
       </c>
-      <c r="J96" s="18"/>
-      <c r="K96" s="19"/>
+      <c r="J96" s="19"/>
+      <c r="K96" s="20"/>
       <c r="N96" s="2">
         <v>45689</v>
       </c>
-      <c r="O96" s="18">
+      <c r="O96" s="19">
         <v>39000</v>
       </c>
-      <c r="P96" s="25"/>
-    </row>
-    <row r="97" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P96" s="24"/>
+    </row>
+    <row r="97" spans="2:18" ht="15.75" customHeight="1">
       <c r="B97" s="2">
         <v>45717</v>
       </c>
-      <c r="C97" s="18">
+      <c r="C97" s="19">
         <v>21990</v>
       </c>
-      <c r="D97" s="19"/>
+      <c r="D97" s="20"/>
       <c r="F97" s="4">
         <f>SUM(C95:D106)</f>
         <v>260000</v>
@@ -3596,226 +3628,226 @@
       <c r="I97" s="2">
         <v>45717</v>
       </c>
-      <c r="J97" s="18">
+      <c r="J97" s="19">
         <f>7400+48000</f>
         <v>55400</v>
       </c>
-      <c r="K97" s="19"/>
+      <c r="K97" s="20"/>
       <c r="N97" s="2">
         <v>45717</v>
       </c>
-      <c r="O97" s="18">
+      <c r="O97" s="19">
         <v>39000</v>
       </c>
-      <c r="P97" s="25"/>
-    </row>
-    <row r="98" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P97" s="24"/>
+    </row>
+    <row r="98" spans="2:18" ht="15.75" customHeight="1">
       <c r="B98" s="2">
         <v>45748</v>
       </c>
-      <c r="C98" s="18">
+      <c r="C98" s="19">
         <v>21990</v>
       </c>
-      <c r="D98" s="19"/>
+      <c r="D98" s="20"/>
       <c r="I98" s="2">
         <v>45748</v>
       </c>
-      <c r="J98" s="18">
+      <c r="J98" s="19">
         <v>48000</v>
       </c>
-      <c r="K98" s="19"/>
+      <c r="K98" s="20"/>
       <c r="N98" s="2">
         <v>45748</v>
       </c>
-      <c r="O98" s="18">
+      <c r="O98" s="19">
         <v>39000</v>
       </c>
-      <c r="P98" s="25"/>
-    </row>
-    <row r="99" spans="2:18" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P98" s="24"/>
+    </row>
+    <row r="99" spans="2:18" ht="15.6" customHeight="1">
       <c r="B99" s="2">
         <v>45778</v>
       </c>
-      <c r="C99" s="18">
+      <c r="C99" s="19">
         <v>21990</v>
       </c>
-      <c r="D99" s="19"/>
+      <c r="D99" s="20"/>
       <c r="I99" s="2">
         <v>45778</v>
       </c>
-      <c r="J99" s="18"/>
-      <c r="K99" s="19"/>
+      <c r="J99" s="19"/>
+      <c r="K99" s="20"/>
       <c r="N99" s="2">
         <v>45778</v>
       </c>
-      <c r="O99" s="18">
+      <c r="O99" s="19">
         <v>39000</v>
       </c>
-      <c r="P99" s="25"/>
-    </row>
-    <row r="100" spans="2:18" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P99" s="24"/>
+    </row>
+    <row r="100" spans="2:18" ht="15.6" customHeight="1">
       <c r="B100" s="2">
         <v>45809</v>
       </c>
-      <c r="C100" s="18">
+      <c r="C100" s="19">
         <v>21840</v>
       </c>
-      <c r="D100" s="19"/>
+      <c r="D100" s="20"/>
       <c r="I100" s="2">
         <v>45809</v>
       </c>
-      <c r="J100" s="18">
+      <c r="J100" s="19">
         <v>48000</v>
       </c>
-      <c r="K100" s="19"/>
+      <c r="K100" s="20"/>
       <c r="N100" s="2">
         <v>45809</v>
       </c>
-      <c r="O100" s="18">
+      <c r="O100" s="19">
         <v>39750</v>
       </c>
-      <c r="P100" s="25"/>
-    </row>
-    <row r="101" spans="2:18" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P100" s="24"/>
+    </row>
+    <row r="101" spans="2:18" ht="15.6" customHeight="1">
       <c r="B101" s="2">
         <v>45839</v>
       </c>
-      <c r="C101" s="18">
+      <c r="C101" s="19">
         <v>21840</v>
       </c>
-      <c r="D101" s="19"/>
+      <c r="D101" s="20"/>
       <c r="I101" s="2">
         <v>45839</v>
       </c>
-      <c r="J101" s="18"/>
-      <c r="K101" s="19"/>
+      <c r="J101" s="19"/>
+      <c r="K101" s="20"/>
       <c r="N101" s="2">
         <v>45839</v>
       </c>
-      <c r="O101" s="18">
+      <c r="O101" s="19">
         <v>39000</v>
       </c>
-      <c r="P101" s="25"/>
-    </row>
-    <row r="102" spans="2:18" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P101" s="24"/>
+    </row>
+    <row r="102" spans="2:18" ht="15.6" customHeight="1">
       <c r="B102" s="2">
         <v>45870</v>
       </c>
-      <c r="C102" s="18">
+      <c r="C102" s="19">
         <v>21540</v>
       </c>
-      <c r="D102" s="19"/>
+      <c r="D102" s="20"/>
       <c r="I102" s="2">
         <v>45870</v>
       </c>
-      <c r="J102" s="18"/>
-      <c r="K102" s="19"/>
+      <c r="J102" s="19"/>
+      <c r="K102" s="20"/>
       <c r="N102" s="2">
         <v>45870</v>
       </c>
-      <c r="O102" s="18">
+      <c r="O102" s="19">
         <v>39000</v>
       </c>
-      <c r="P102" s="25"/>
-    </row>
-    <row r="103" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="P102" s="24"/>
+    </row>
+    <row r="103" spans="2:18" ht="14.45">
       <c r="B103" s="2">
         <v>45901</v>
       </c>
-      <c r="C103" s="18">
+      <c r="C103" s="19">
         <v>21690</v>
       </c>
-      <c r="D103" s="19"/>
+      <c r="D103" s="20"/>
       <c r="I103" s="2">
         <v>45901</v>
       </c>
-      <c r="J103" s="18">
+      <c r="J103" s="19">
         <v>48000</v>
       </c>
-      <c r="K103" s="19"/>
+      <c r="K103" s="20"/>
       <c r="N103" s="2">
         <v>45901</v>
       </c>
-      <c r="O103" s="18">
+      <c r="O103" s="19">
         <v>39000</v>
       </c>
-      <c r="P103" s="25"/>
-    </row>
-    <row r="104" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="P103" s="24"/>
+    </row>
+    <row r="104" spans="2:18" ht="14.45">
       <c r="B104" s="2">
         <v>45931</v>
       </c>
-      <c r="C104" s="18">
+      <c r="C104" s="19">
         <v>18490</v>
       </c>
-      <c r="D104" s="19"/>
+      <c r="D104" s="20"/>
       <c r="I104" s="2">
         <v>45931</v>
       </c>
-      <c r="J104" s="18"/>
-      <c r="K104" s="19"/>
+      <c r="J104" s="19"/>
+      <c r="K104" s="20"/>
       <c r="N104" s="2">
         <v>45931</v>
       </c>
-      <c r="O104" s="18">
+      <c r="O104" s="19">
         <v>39000</v>
       </c>
-      <c r="P104" s="25"/>
-    </row>
-    <row r="105" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="P104" s="24"/>
+    </row>
+    <row r="105" spans="2:18" ht="14.45">
       <c r="B105" s="2">
         <v>45962</v>
       </c>
-      <c r="C105" s="18">
+      <c r="C105" s="19">
         <v>22700</v>
       </c>
-      <c r="D105" s="19"/>
+      <c r="D105" s="20"/>
       <c r="I105" s="2">
         <v>45962</v>
       </c>
-      <c r="J105" s="18"/>
-      <c r="K105" s="19"/>
+      <c r="J105" s="19"/>
+      <c r="K105" s="20"/>
       <c r="N105" s="2">
         <v>45962</v>
       </c>
-      <c r="O105" s="18">
+      <c r="O105" s="19">
         <v>39000</v>
       </c>
-      <c r="P105" s="19"/>
-    </row>
-    <row r="106" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P105" s="20"/>
+    </row>
+    <row r="106" spans="2:18" ht="15" customHeight="1">
       <c r="B106" s="2">
         <v>45992</v>
       </c>
-      <c r="C106" s="18">
+      <c r="C106" s="19">
         <v>22250</v>
       </c>
-      <c r="D106" s="19"/>
+      <c r="D106" s="20"/>
       <c r="I106" s="2">
         <v>45992</v>
       </c>
-      <c r="J106" s="18"/>
-      <c r="K106" s="19"/>
+      <c r="J106" s="19"/>
+      <c r="K106" s="20"/>
       <c r="N106" s="2">
         <v>45992</v>
       </c>
-      <c r="O106" s="18">
+      <c r="O106" s="19">
         <v>39000</v>
       </c>
-      <c r="P106" s="19"/>
-    </row>
-    <row r="107" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="P106" s="20"/>
+    </row>
+    <row r="107" spans="2:18" ht="14.45">
       <c r="B107" s="9"/>
       <c r="C107" s="5"/>
       <c r="D107" s="5"/>
       <c r="I107" t="s">
         <v>12</v>
       </c>
-      <c r="J107" s="23">
+      <c r="J107" s="26">
         <f>J97+J98+J100+J103</f>
         <v>199400</v>
       </c>
-      <c r="K107" s="24"/>
+      <c r="K107" s="27"/>
       <c r="N107" t="s">
         <v>12</v>
       </c>
@@ -3825,422 +3857,538 @@
       </c>
       <c r="R107" s="4"/>
     </row>
-    <row r="108" spans="2:18" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="2:18" ht="14.45" customHeight="1">
       <c r="B108" s="9"/>
       <c r="C108" s="5"/>
       <c r="D108" s="5"/>
     </row>
-    <row r="109" spans="2:18" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="2:18" ht="14.45" customHeight="1">
       <c r="B109" s="9"/>
       <c r="C109" s="5"/>
       <c r="D109" s="5"/>
     </row>
-    <row r="110" spans="2:18" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="2:18" ht="14.45" customHeight="1">
       <c r="B110" s="9"/>
       <c r="C110" s="5"/>
       <c r="D110" s="5"/>
     </row>
-    <row r="111" spans="2:18" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B111" s="15" t="s">
+    <row r="111" spans="2:18" ht="14.45" customHeight="1">
+      <c r="B111" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="C111" s="16"/>
-      <c r="D111" s="17"/>
-    </row>
-    <row r="112" spans="2:18" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C111" s="22"/>
+      <c r="D111" s="23"/>
+    </row>
+    <row r="112" spans="2:18" ht="14.45" customHeight="1">
       <c r="B112" s="2">
         <v>45658</v>
       </c>
-      <c r="C112" s="18">
+      <c r="C112" s="19">
         <v>16501</v>
       </c>
-      <c r="D112" s="25"/>
+      <c r="D112" s="24"/>
       <c r="E112" s="4"/>
     </row>
-    <row r="113" spans="2:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="2:6" ht="14.45" customHeight="1">
       <c r="B113" s="2">
         <v>45689</v>
       </c>
-      <c r="C113" s="18">
+      <c r="C113" s="19">
         <v>15146</v>
       </c>
-      <c r="D113" s="25"/>
+      <c r="D113" s="24"/>
       <c r="E113" s="4"/>
     </row>
-    <row r="114" spans="2:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="2:6" ht="14.45" customHeight="1">
       <c r="B114" s="2">
         <v>45717</v>
       </c>
-      <c r="C114" s="18">
+      <c r="C114" s="19">
         <v>16218</v>
       </c>
-      <c r="D114" s="19"/>
+      <c r="D114" s="20"/>
       <c r="E114" s="4"/>
     </row>
-    <row r="115" spans="2:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="2:6" ht="14.45" customHeight="1">
       <c r="B115" s="2">
         <v>45748</v>
       </c>
-      <c r="C115" s="18">
+      <c r="C115" s="19">
         <v>18093.5</v>
       </c>
-      <c r="D115" s="19"/>
+      <c r="D115" s="20"/>
       <c r="E115" s="4"/>
     </row>
-    <row r="116" spans="2:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="2:6" ht="14.45" customHeight="1">
       <c r="B116" s="2">
         <v>45778</v>
       </c>
-      <c r="C116" s="18">
+      <c r="C116" s="19">
         <v>18454</v>
       </c>
-      <c r="D116" s="19"/>
+      <c r="D116" s="20"/>
       <c r="E116" s="4"/>
     </row>
-    <row r="117" spans="2:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="2:6" ht="14.45" customHeight="1">
       <c r="B117" s="2">
         <v>45809</v>
       </c>
-      <c r="C117" s="18">
+      <c r="C117" s="19">
         <v>17484</v>
       </c>
-      <c r="D117" s="19"/>
+      <c r="D117" s="20"/>
       <c r="E117" s="4"/>
       <c r="F117" s="4">
         <f>SUM(C112:D123)</f>
         <v>215028.5</v>
       </c>
     </row>
-    <row r="118" spans="2:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="2:6" ht="14.45" customHeight="1">
       <c r="B118" s="2">
         <v>45839</v>
       </c>
-      <c r="C118" s="18">
+      <c r="C118" s="19">
         <v>18964</v>
       </c>
-      <c r="D118" s="19"/>
+      <c r="D118" s="20"/>
       <c r="E118" s="4"/>
     </row>
-    <row r="119" spans="2:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="2:6" ht="14.45" customHeight="1">
       <c r="B119" s="2">
         <v>45870</v>
       </c>
-      <c r="C119" s="18">
+      <c r="C119" s="19">
         <v>19732</v>
       </c>
-      <c r="D119" s="19"/>
+      <c r="D119" s="20"/>
       <c r="E119" s="4"/>
     </row>
-    <row r="120" spans="2:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="2:6" ht="14.45" customHeight="1">
       <c r="B120" s="2">
         <v>45901</v>
       </c>
-      <c r="C120" s="18">
+      <c r="C120" s="19">
         <v>18942</v>
       </c>
-      <c r="D120" s="19"/>
+      <c r="D120" s="20"/>
       <c r="E120" s="4"/>
     </row>
-    <row r="121" spans="2:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="2:6" ht="14.45" customHeight="1">
       <c r="B121" s="2">
         <v>45931</v>
       </c>
-      <c r="C121" s="18">
+      <c r="C121" s="19">
         <v>18899</v>
       </c>
-      <c r="D121" s="19"/>
+      <c r="D121" s="20"/>
       <c r="E121" s="4"/>
     </row>
-    <row r="122" spans="2:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="2:6" ht="14.45" customHeight="1">
       <c r="B122" s="2">
         <v>45962</v>
       </c>
-      <c r="C122" s="18">
+      <c r="C122" s="19">
         <v>18800</v>
       </c>
-      <c r="D122" s="19"/>
-    </row>
-    <row r="123" spans="2:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D122" s="20"/>
+    </row>
+    <row r="123" spans="2:6" ht="14.45" customHeight="1">
       <c r="B123" s="2">
         <v>45992</v>
       </c>
-      <c r="C123" s="18">
+      <c r="C123" s="19">
         <v>17795</v>
       </c>
-      <c r="D123" s="19"/>
-    </row>
-    <row r="124" spans="2:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D123" s="20"/>
+    </row>
+    <row r="124" spans="2:6" ht="14.45" customHeight="1">
       <c r="B124" s="9"/>
       <c r="C124" s="5"/>
       <c r="D124" s="5"/>
     </row>
-    <row r="125" spans="2:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="2:6" ht="14.45" customHeight="1">
       <c r="B125" s="9"/>
       <c r="C125" s="5"/>
       <c r="D125" s="5"/>
     </row>
-    <row r="126" spans="2:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="2:6" ht="14.45" customHeight="1">
       <c r="B126" s="9"/>
       <c r="C126" s="5"/>
       <c r="D126" s="5"/>
     </row>
-    <row r="127" spans="2:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B127" s="15" t="s">
+    <row r="127" spans="2:6" ht="14.45" customHeight="1">
+      <c r="B127" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="C127" s="16"/>
-      <c r="D127" s="17"/>
-    </row>
-    <row r="128" spans="2:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C127" s="22"/>
+      <c r="D127" s="23"/>
+    </row>
+    <row r="128" spans="2:6" ht="14.45" customHeight="1">
       <c r="B128" s="2">
         <v>45658</v>
       </c>
-      <c r="C128" s="18">
+      <c r="C128" s="19">
         <v>26868.14</v>
       </c>
-      <c r="D128" s="25"/>
-    </row>
-    <row r="129" spans="2:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D128" s="24"/>
+    </row>
+    <row r="129" spans="2:6" ht="14.45" customHeight="1">
       <c r="B129" s="2">
         <v>45689</v>
       </c>
-      <c r="C129" s="18">
+      <c r="C129" s="19">
         <v>25931.19</v>
       </c>
-      <c r="D129" s="25"/>
-    </row>
-    <row r="130" spans="2:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D129" s="24"/>
+    </row>
+    <row r="130" spans="2:6" ht="14.45" customHeight="1">
       <c r="B130" s="2">
         <v>45717</v>
       </c>
-      <c r="C130" s="18">
+      <c r="C130" s="19">
         <v>31296.94</v>
       </c>
-      <c r="D130" s="19"/>
+      <c r="D130" s="20"/>
       <c r="F130" s="4">
         <f>SUM(C128:D139)</f>
         <v>412566.35</v>
       </c>
     </row>
-    <row r="131" spans="2:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="2:6" ht="14.45" customHeight="1">
       <c r="B131" s="2">
         <v>45748</v>
       </c>
-      <c r="C131" s="18">
+      <c r="C131" s="19">
         <v>32586.6</v>
       </c>
-      <c r="D131" s="19"/>
-    </row>
-    <row r="132" spans="2:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D131" s="20"/>
+    </row>
+    <row r="132" spans="2:6" ht="14.45" customHeight="1">
       <c r="B132" s="2">
         <v>45778</v>
       </c>
-      <c r="C132" s="18">
+      <c r="C132" s="19">
         <v>36187.5</v>
       </c>
-      <c r="D132" s="19"/>
-    </row>
-    <row r="133" spans="2:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D132" s="20"/>
+    </row>
+    <row r="133" spans="2:6" ht="14.45" customHeight="1">
       <c r="B133" s="2">
         <v>45809</v>
       </c>
-      <c r="C133" s="18">
+      <c r="C133" s="19">
         <v>39677.050000000003</v>
       </c>
-      <c r="D133" s="19"/>
-    </row>
-    <row r="134" spans="2:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D133" s="20"/>
+    </row>
+    <row r="134" spans="2:6" ht="14.45" customHeight="1">
       <c r="B134" s="2">
         <v>45839</v>
       </c>
-      <c r="C134" s="18">
+      <c r="C134" s="19">
         <v>48703.25</v>
       </c>
-      <c r="D134" s="19"/>
-    </row>
-    <row r="135" spans="2:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D134" s="20"/>
+    </row>
+    <row r="135" spans="2:6" ht="14.45" customHeight="1">
       <c r="B135" s="2">
         <v>45870</v>
       </c>
-      <c r="C135" s="18">
+      <c r="C135" s="19">
         <v>44995.199999999997</v>
       </c>
-      <c r="D135" s="19"/>
-    </row>
-    <row r="136" spans="2:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D135" s="20"/>
+    </row>
+    <row r="136" spans="2:6" ht="14.45" customHeight="1">
       <c r="B136" s="2">
         <v>45901</v>
       </c>
-      <c r="C136" s="18">
+      <c r="C136" s="19">
         <v>43215.42</v>
       </c>
-      <c r="D136" s="19"/>
-    </row>
-    <row r="137" spans="2:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D136" s="20"/>
+    </row>
+    <row r="137" spans="2:6" ht="14.45" customHeight="1">
       <c r="B137" s="2">
         <v>45931</v>
       </c>
-      <c r="C137" s="18">
+      <c r="C137" s="19">
         <v>32273.79</v>
       </c>
-      <c r="D137" s="19"/>
-    </row>
-    <row r="138" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="D137" s="20"/>
+    </row>
+    <row r="138" spans="2:6" ht="14.45">
       <c r="B138" s="2">
         <v>45962</v>
       </c>
-      <c r="C138" s="18">
+      <c r="C138" s="19">
         <v>14562.02</v>
       </c>
-      <c r="D138" s="19"/>
-    </row>
-    <row r="139" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="D138" s="20"/>
+    </row>
+    <row r="139" spans="2:6" ht="14.45">
       <c r="B139" s="2">
         <v>45992</v>
       </c>
-      <c r="C139" s="18">
+      <c r="C139" s="19">
         <v>36269.25</v>
       </c>
-      <c r="D139" s="19"/>
-    </row>
-    <row r="140" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="D139" s="20"/>
+    </row>
+    <row r="140" spans="2:6" ht="14.45">
       <c r="B140" s="9"/>
       <c r="C140" s="5"/>
       <c r="D140" s="5"/>
     </row>
-    <row r="141" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="141" spans="2:6" ht="14.45">
       <c r="B141" s="9"/>
       <c r="C141" s="5"/>
       <c r="D141" s="5"/>
     </row>
-    <row r="142" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="142" spans="2:6" ht="14.45">
       <c r="B142" s="9"/>
       <c r="C142" s="5"/>
       <c r="D142" s="5"/>
     </row>
-    <row r="143" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B143" s="15" t="s">
+    <row r="143" spans="2:6" ht="14.45">
+      <c r="B143" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="C143" s="16"/>
-      <c r="D143" s="17"/>
-    </row>
-    <row r="144" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C143" s="22"/>
+      <c r="D143" s="23"/>
+    </row>
+    <row r="144" spans="2:6" ht="14.45">
       <c r="B144" s="2">
         <v>45658</v>
       </c>
-      <c r="C144" s="18"/>
-      <c r="D144" s="25"/>
-    </row>
-    <row r="145" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C144" s="19"/>
+      <c r="D144" s="24"/>
+    </row>
+    <row r="145" spans="2:6" ht="14.45">
       <c r="B145" s="2">
         <v>45689</v>
       </c>
-      <c r="C145" s="18"/>
-      <c r="D145" s="25"/>
-    </row>
-    <row r="146" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C145" s="19"/>
+      <c r="D145" s="24"/>
+    </row>
+    <row r="146" spans="2:6" ht="14.45">
       <c r="B146" s="2">
         <v>45717</v>
       </c>
-      <c r="C146" s="18"/>
-      <c r="D146" s="19"/>
-    </row>
-    <row r="147" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C146" s="19"/>
+      <c r="D146" s="20"/>
+    </row>
+    <row r="147" spans="2:6" ht="14.45">
       <c r="B147" s="2">
         <v>45748</v>
       </c>
-      <c r="C147" s="18"/>
-      <c r="D147" s="19"/>
-    </row>
-    <row r="148" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C147" s="19"/>
+      <c r="D147" s="20"/>
+    </row>
+    <row r="148" spans="2:6" ht="14.45">
       <c r="B148" s="2">
         <v>45778</v>
       </c>
-      <c r="C148" s="18"/>
-      <c r="D148" s="19"/>
-    </row>
-    <row r="149" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C148" s="19"/>
+      <c r="D148" s="20"/>
+    </row>
+    <row r="149" spans="2:6" ht="14.45">
       <c r="B149" s="2">
         <v>45809</v>
       </c>
-      <c r="C149" s="18"/>
-      <c r="D149" s="19"/>
+      <c r="C149" s="19"/>
+      <c r="D149" s="20"/>
       <c r="F149" s="4">
         <f>SUM(C144:D155)</f>
         <v>56200</v>
       </c>
     </row>
-    <row r="150" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="150" spans="2:6" ht="14.45">
       <c r="B150" s="2">
         <v>45839</v>
       </c>
-      <c r="C150" s="18">
+      <c r="C150" s="19">
         <v>52771</v>
       </c>
-      <c r="D150" s="19"/>
-    </row>
-    <row r="151" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="D150" s="20"/>
+    </row>
+    <row r="151" spans="2:6" ht="14.45">
       <c r="B151" s="2">
         <v>45870</v>
       </c>
-      <c r="C151" s="18"/>
-      <c r="D151" s="19"/>
-    </row>
-    <row r="152" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C151" s="19"/>
+      <c r="D151" s="20"/>
+    </row>
+    <row r="152" spans="2:6" ht="14.45">
       <c r="B152" s="2">
         <v>45901</v>
       </c>
-      <c r="C152" s="18"/>
-      <c r="D152" s="19"/>
-    </row>
-    <row r="153" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C152" s="19"/>
+      <c r="D152" s="20"/>
+    </row>
+    <row r="153" spans="2:6" ht="14.45">
       <c r="B153" s="2">
         <v>45931</v>
       </c>
-      <c r="C153" s="18"/>
-      <c r="D153" s="19"/>
-    </row>
-    <row r="154" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C153" s="19"/>
+      <c r="D153" s="20"/>
+    </row>
+    <row r="154" spans="2:6" ht="14.45">
       <c r="B154" s="2">
         <v>45962</v>
       </c>
-      <c r="C154" s="18">
+      <c r="C154" s="19">
         <v>2934</v>
       </c>
-      <c r="D154" s="19"/>
-    </row>
-    <row r="155" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="D154" s="20"/>
+    </row>
+    <row r="155" spans="2:6" ht="14.45">
       <c r="B155" s="2">
         <v>45992</v>
       </c>
-      <c r="C155" s="18">
+      <c r="C155" s="19">
         <v>495</v>
       </c>
-      <c r="D155" s="19"/>
-    </row>
-    <row r="162" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="D155" s="20"/>
+    </row>
+    <row r="162" spans="2:4" ht="14.45">
       <c r="B162" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C162" s="21">
+        <v>20</v>
+      </c>
+      <c r="C162" s="28">
         <f>SUM(F9+F22+F37+F52+F67+F82+F97+F117+F130+F149+J107+O107)</f>
         <v>3272751.773</v>
       </c>
-      <c r="D162" s="22"/>
+      <c r="D162" s="29"/>
     </row>
   </sheetData>
   <mergeCells count="160">
-    <mergeCell ref="C148:D148"/>
-    <mergeCell ref="C149:D149"/>
-    <mergeCell ref="C150:D150"/>
-    <mergeCell ref="C151:D151"/>
-    <mergeCell ref="C152:D152"/>
-    <mergeCell ref="C153:D153"/>
-    <mergeCell ref="C154:D154"/>
-    <mergeCell ref="C162:D162"/>
-    <mergeCell ref="B143:D143"/>
-    <mergeCell ref="C155:D155"/>
+    <mergeCell ref="C118:D118"/>
+    <mergeCell ref="C119:D119"/>
+    <mergeCell ref="C120:D120"/>
+    <mergeCell ref="B111:D111"/>
+    <mergeCell ref="C121:D121"/>
+    <mergeCell ref="C122:D122"/>
+    <mergeCell ref="C123:D123"/>
+    <mergeCell ref="C101:D101"/>
+    <mergeCell ref="C102:D102"/>
+    <mergeCell ref="C103:D103"/>
+    <mergeCell ref="C112:D112"/>
+    <mergeCell ref="C113:D113"/>
+    <mergeCell ref="C114:D114"/>
+    <mergeCell ref="C115:D115"/>
+    <mergeCell ref="C116:D116"/>
+    <mergeCell ref="C117:D117"/>
+    <mergeCell ref="C136:D136"/>
+    <mergeCell ref="C137:D137"/>
+    <mergeCell ref="C138:D138"/>
+    <mergeCell ref="C139:D139"/>
+    <mergeCell ref="C145:D145"/>
+    <mergeCell ref="C130:D130"/>
+    <mergeCell ref="C131:D131"/>
+    <mergeCell ref="C132:D132"/>
+    <mergeCell ref="C133:D133"/>
+    <mergeCell ref="C134:D134"/>
+    <mergeCell ref="C135:D135"/>
+    <mergeCell ref="C90:D90"/>
+    <mergeCell ref="C91:D91"/>
+    <mergeCell ref="B94:D94"/>
+    <mergeCell ref="C95:D95"/>
+    <mergeCell ref="C96:D96"/>
+    <mergeCell ref="C97:D97"/>
+    <mergeCell ref="C84:D84"/>
+    <mergeCell ref="C85:D85"/>
+    <mergeCell ref="C86:D86"/>
+    <mergeCell ref="C87:D87"/>
+    <mergeCell ref="C88:D88"/>
+    <mergeCell ref="C89:D89"/>
+    <mergeCell ref="C76:D76"/>
+    <mergeCell ref="B79:D79"/>
+    <mergeCell ref="C80:D80"/>
+    <mergeCell ref="C81:D81"/>
+    <mergeCell ref="C82:D82"/>
+    <mergeCell ref="C83:D83"/>
+    <mergeCell ref="C70:D70"/>
+    <mergeCell ref="C71:D71"/>
+    <mergeCell ref="C72:D72"/>
+    <mergeCell ref="C73:D73"/>
+    <mergeCell ref="C74:D74"/>
+    <mergeCell ref="C75:D75"/>
+    <mergeCell ref="B64:D64"/>
+    <mergeCell ref="C65:D65"/>
+    <mergeCell ref="C66:D66"/>
+    <mergeCell ref="C67:D67"/>
+    <mergeCell ref="C68:D68"/>
+    <mergeCell ref="C69:D69"/>
+    <mergeCell ref="C56:D56"/>
+    <mergeCell ref="C57:D57"/>
+    <mergeCell ref="C58:D58"/>
+    <mergeCell ref="C59:D59"/>
+    <mergeCell ref="C60:D60"/>
+    <mergeCell ref="C61:D61"/>
+    <mergeCell ref="C52:D52"/>
+    <mergeCell ref="C53:D53"/>
+    <mergeCell ref="C54:D54"/>
+    <mergeCell ref="C55:D55"/>
+    <mergeCell ref="C42:D42"/>
+    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="C44:D44"/>
+    <mergeCell ref="C45:D45"/>
+    <mergeCell ref="C46:D46"/>
+    <mergeCell ref="B49:D49"/>
+    <mergeCell ref="C41:D41"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="C50:D50"/>
+    <mergeCell ref="C51:D51"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="C40:D40"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="N94:P94"/>
+    <mergeCell ref="O95:P95"/>
+    <mergeCell ref="I94:K94"/>
+    <mergeCell ref="J95:K95"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="O105:P105"/>
+    <mergeCell ref="O106:P106"/>
+    <mergeCell ref="O96:P96"/>
+    <mergeCell ref="O97:P97"/>
+    <mergeCell ref="O98:P98"/>
+    <mergeCell ref="O99:P99"/>
+    <mergeCell ref="O100:P100"/>
+    <mergeCell ref="O101:P101"/>
+    <mergeCell ref="O102:P102"/>
+    <mergeCell ref="O103:P103"/>
+    <mergeCell ref="O104:P104"/>
     <mergeCell ref="J105:K105"/>
     <mergeCell ref="J106:K106"/>
     <mergeCell ref="J107:K107"/>
@@ -4265,137 +4413,20 @@
     <mergeCell ref="C98:D98"/>
     <mergeCell ref="C99:D99"/>
     <mergeCell ref="C100:D100"/>
-    <mergeCell ref="O105:P105"/>
-    <mergeCell ref="O106:P106"/>
-    <mergeCell ref="O96:P96"/>
-    <mergeCell ref="O97:P97"/>
-    <mergeCell ref="O98:P98"/>
-    <mergeCell ref="O99:P99"/>
-    <mergeCell ref="O100:P100"/>
-    <mergeCell ref="O101:P101"/>
-    <mergeCell ref="O102:P102"/>
-    <mergeCell ref="O103:P103"/>
-    <mergeCell ref="O104:P104"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="N94:P94"/>
-    <mergeCell ref="O95:P95"/>
-    <mergeCell ref="I94:K94"/>
-    <mergeCell ref="J95:K95"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="C38:D38"/>
-    <mergeCell ref="C39:D39"/>
-    <mergeCell ref="C40:D40"/>
-    <mergeCell ref="C41:D41"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="C50:D50"/>
-    <mergeCell ref="C51:D51"/>
-    <mergeCell ref="C52:D52"/>
-    <mergeCell ref="C53:D53"/>
-    <mergeCell ref="C54:D54"/>
-    <mergeCell ref="C55:D55"/>
-    <mergeCell ref="C42:D42"/>
-    <mergeCell ref="C43:D43"/>
-    <mergeCell ref="C44:D44"/>
-    <mergeCell ref="C45:D45"/>
-    <mergeCell ref="C46:D46"/>
-    <mergeCell ref="B49:D49"/>
-    <mergeCell ref="B64:D64"/>
-    <mergeCell ref="C65:D65"/>
-    <mergeCell ref="C66:D66"/>
-    <mergeCell ref="C67:D67"/>
-    <mergeCell ref="C68:D68"/>
-    <mergeCell ref="C69:D69"/>
-    <mergeCell ref="C56:D56"/>
-    <mergeCell ref="C57:D57"/>
-    <mergeCell ref="C58:D58"/>
-    <mergeCell ref="C59:D59"/>
-    <mergeCell ref="C60:D60"/>
-    <mergeCell ref="C61:D61"/>
-    <mergeCell ref="C76:D76"/>
-    <mergeCell ref="B79:D79"/>
-    <mergeCell ref="C80:D80"/>
-    <mergeCell ref="C81:D81"/>
-    <mergeCell ref="C82:D82"/>
-    <mergeCell ref="C83:D83"/>
-    <mergeCell ref="C70:D70"/>
-    <mergeCell ref="C71:D71"/>
-    <mergeCell ref="C72:D72"/>
-    <mergeCell ref="C73:D73"/>
-    <mergeCell ref="C74:D74"/>
-    <mergeCell ref="C75:D75"/>
-    <mergeCell ref="C90:D90"/>
-    <mergeCell ref="C91:D91"/>
-    <mergeCell ref="B94:D94"/>
-    <mergeCell ref="C95:D95"/>
-    <mergeCell ref="C96:D96"/>
-    <mergeCell ref="C97:D97"/>
-    <mergeCell ref="C84:D84"/>
-    <mergeCell ref="C85:D85"/>
-    <mergeCell ref="C86:D86"/>
-    <mergeCell ref="C87:D87"/>
-    <mergeCell ref="C88:D88"/>
-    <mergeCell ref="C89:D89"/>
-    <mergeCell ref="C136:D136"/>
-    <mergeCell ref="C137:D137"/>
-    <mergeCell ref="C138:D138"/>
-    <mergeCell ref="C139:D139"/>
-    <mergeCell ref="C145:D145"/>
-    <mergeCell ref="C130:D130"/>
-    <mergeCell ref="C131:D131"/>
-    <mergeCell ref="C132:D132"/>
-    <mergeCell ref="C133:D133"/>
-    <mergeCell ref="C134:D134"/>
-    <mergeCell ref="C135:D135"/>
-    <mergeCell ref="C118:D118"/>
-    <mergeCell ref="C119:D119"/>
-    <mergeCell ref="C120:D120"/>
-    <mergeCell ref="B111:D111"/>
-    <mergeCell ref="C121:D121"/>
-    <mergeCell ref="C122:D122"/>
-    <mergeCell ref="C123:D123"/>
-    <mergeCell ref="C101:D101"/>
-    <mergeCell ref="C102:D102"/>
-    <mergeCell ref="C103:D103"/>
-    <mergeCell ref="C112:D112"/>
-    <mergeCell ref="C113:D113"/>
-    <mergeCell ref="C114:D114"/>
-    <mergeCell ref="C115:D115"/>
-    <mergeCell ref="C116:D116"/>
-    <mergeCell ref="C117:D117"/>
+    <mergeCell ref="C148:D148"/>
+    <mergeCell ref="C149:D149"/>
+    <mergeCell ref="C150:D150"/>
+    <mergeCell ref="C151:D151"/>
+    <mergeCell ref="C152:D152"/>
+    <mergeCell ref="C153:D153"/>
+    <mergeCell ref="C154:D154"/>
+    <mergeCell ref="C162:D162"/>
+    <mergeCell ref="B143:D143"/>
+    <mergeCell ref="C155:D155"/>
   </mergeCells>
   <conditionalFormatting sqref="B18">
     <cfRule type="uniqueValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>